--- a/commercial/outputs/Commercial_Deal_Dashboard.xlsx
+++ b/commercial/outputs/Commercial_Deal_Dashboard.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="367">
   <si>
     <t>Commercial Deal Dashboard — Fort Lauderdale</t>
   </si>
@@ -143,15 +143,33 @@
     <t>Implied cap</t>
   </si>
   <si>
+    <t>Mkt rent (comps)</t>
+  </si>
+  <si>
+    <t>Conf</t>
+  </si>
+  <si>
     <t>Multifamily</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Office</t>
   </si>
   <si>
+    <t>Indicative</t>
+  </si>
+  <si>
     <t>Retail</t>
   </si>
   <si>
+    <t>Med</t>
+  </si>
+  <si>
     <t>Industrial</t>
   </si>
   <si>
@@ -173,6 +191,9 @@
     <t>Commercial (other)</t>
   </si>
   <si>
+    <t>'Mkt rent (comps)' is the median asking lease rate from the lease listings — where present, consider replacing the assumed Rent $/SqFt with it.</t>
+  </si>
+  <si>
     <t>Submarkets — normalized $/SqFt</t>
   </si>
   <si>
@@ -212,9 +233,6 @@
     <t>Area 3810</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Area 3380</t>
   </si>
   <si>
@@ -249,6 +267,9 @@
   </si>
   <si>
     <t>Sold</t>
+  </si>
+  <si>
+    <t>Mkt rent</t>
   </si>
   <si>
     <t>Vac</t>
@@ -1313,13 +1334,13 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1789,12 +1810,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1807,39 +1828,39 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D5" s="16">
         <v>1500</v>
@@ -1853,19 +1874,19 @@
       <c r="G5" s="8">
         <v>597</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <v>2.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" s="16">
         <v>13402</v>
@@ -1879,19 +1900,19 @@
       <c r="G6" s="8">
         <v>134</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <v>-14.8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" s="16">
         <v>12500</v>
@@ -1905,25 +1926,25 @@
       <c r="G7" s="8">
         <v>216</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <v>156.1</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D8" s="16">
         <v>1938</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>62</v>
+      <c r="E8" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="F8" s="8">
         <v>325000</v>
@@ -1931,19 +1952,19 @@
       <c r="G8" s="8">
         <v>168</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <v>-28.7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D9" s="16">
         <v>5200</v>
@@ -1957,25 +1978,25 @@
       <c r="G9" s="8">
         <v>38</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <v>-40.4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D10" s="16">
         <v>1938</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>62</v>
+      <c r="E10" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="8">
         <v>185000</v>
@@ -1983,19 +2004,19 @@
       <c r="G10" s="8">
         <v>95</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <v>-59.4</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D11" s="16">
         <v>10289</v>
@@ -2009,19 +2030,19 @@
       <c r="G11" s="8">
         <v>131</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <v>-37.1</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D12" s="16">
         <v>36491</v>
@@ -2035,19 +2056,19 @@
       <c r="G12" s="8">
         <v>96</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <v>39.8</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D13" s="16">
         <v>17001</v>
@@ -2061,19 +2082,19 @@
       <c r="G13" s="8">
         <v>203</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <v>41.3</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" s="16">
         <v>22496</v>
@@ -2087,19 +2108,19 @@
       <c r="G14" s="8">
         <v>120</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" s="16">
         <v>12960</v>
@@ -2113,19 +2134,19 @@
       <c r="G15" s="8">
         <v>197</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <v>22.7</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" s="16">
         <v>6750</v>
@@ -2139,19 +2160,19 @@
       <c r="G16" s="8">
         <v>150</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <v>-33.7</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="16">
         <v>5500</v>
@@ -2165,19 +2186,19 @@
       <c r="G17" s="8">
         <v>355</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <v>40.1</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="16">
         <v>5500</v>
@@ -2191,19 +2212,19 @@
       <c r="G18" s="8">
         <v>324</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="14">
         <v>27.9</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" s="16">
         <v>6192</v>
@@ -2217,19 +2238,19 @@
       <c r="G19" s="8">
         <v>193</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="14">
         <v>-18.7</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" s="16">
         <v>11349</v>
@@ -2243,19 +2264,19 @@
       <c r="G20" s="8">
         <v>95</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="14">
         <v>-44.7</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D21" s="16">
         <v>11736</v>
@@ -2269,19 +2290,19 @@
       <c r="G21" s="8">
         <v>134</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <v>-31</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D22" s="16">
         <v>10000</v>
@@ -2295,19 +2316,19 @@
       <c r="G22" s="8">
         <v>108</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="14">
         <v>-49.2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D23" s="16">
         <v>13683</v>
@@ -2321,19 +2342,19 @@
       <c r="G23" s="8">
         <v>190</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="14">
         <v>25.7</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D24" s="16">
         <v>9998</v>
@@ -2347,19 +2368,19 @@
       <c r="G24" s="8">
         <v>177</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="14">
         <v>-4.3</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D25" s="16">
         <v>16500</v>
@@ -2373,19 +2394,19 @@
       <c r="G25" s="8">
         <v>105</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="14">
         <v>-26.1</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D26" s="16">
         <v>11662</v>
@@ -2399,19 +2420,19 @@
       <c r="G26" s="8">
         <v>120</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="14">
         <v>-27.1</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D27" s="16">
         <v>11662</v>
@@ -2425,19 +2446,19 @@
       <c r="G27" s="8">
         <v>117</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="14">
         <v>-31</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D28" s="16">
         <v>6003</v>
@@ -2451,19 +2472,19 @@
       <c r="G28" s="8">
         <v>200</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="14">
         <v>-14.7</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D29" s="16">
         <v>3429</v>
@@ -2477,19 +2498,19 @@
       <c r="G29" s="8">
         <v>343</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="14">
         <v>5.1</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D30" s="16">
         <v>6110</v>
@@ -2503,19 +2524,19 @@
       <c r="G30" s="8">
         <v>188</v>
       </c>
-      <c r="H30" s="13">
+      <c r="H30" s="14">
         <v>20.9</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D31" s="16">
         <v>9828</v>
@@ -2529,19 +2550,19 @@
       <c r="G31" s="8">
         <v>113</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="14">
         <v>-39.3</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D32" s="16">
         <v>7004</v>
@@ -2555,19 +2576,19 @@
       <c r="G32" s="8">
         <v>126</v>
       </c>
-      <c r="H32" s="13">
+      <c r="H32" s="14">
         <v>-41.4</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D33" s="16">
         <v>1258</v>
@@ -2581,19 +2602,19 @@
       <c r="G33" s="8">
         <v>461</v>
       </c>
-      <c r="H33" s="13">
+      <c r="H33" s="14">
         <v>-17.4</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="16">
         <v>35087</v>
@@ -2607,19 +2628,19 @@
       <c r="G34" s="8">
         <v>180</v>
       </c>
-      <c r="H34" s="13">
+      <c r="H34" s="14">
         <v>51.1</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D35" s="16">
         <v>7960</v>
@@ -2633,19 +2654,19 @@
       <c r="G35" s="8">
         <v>270</v>
       </c>
-      <c r="H35" s="13">
+      <c r="H35" s="14">
         <v>35.2</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D36" s="16">
         <v>13512</v>
@@ -2659,19 +2680,19 @@
       <c r="G36" s="8">
         <v>152</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="14">
         <v>-22.9</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D37" s="16">
         <v>11480</v>
@@ -2685,19 +2706,19 @@
       <c r="G37" s="8">
         <v>152</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="14">
         <v>-29.2</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D38" s="16">
         <v>6752</v>
@@ -2711,19 +2732,19 @@
       <c r="G38" s="8">
         <v>170</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="14">
         <v>-40.3</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D39" s="16">
         <v>1276</v>
@@ -2737,19 +2758,19 @@
       <c r="G39" s="8">
         <v>451</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="14">
         <v>-37.3</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D40" s="16">
         <v>25024</v>
@@ -2763,19 +2784,19 @@
       <c r="G40" s="8">
         <v>180</v>
       </c>
-      <c r="H40" s="13">
+      <c r="H40" s="14">
         <v>53.8</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D41" s="16">
         <v>6250</v>
@@ -2789,19 +2810,19 @@
       <c r="G41" s="8">
         <v>182</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H41" s="14">
         <v>0.9</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D42" s="16">
         <v>20250</v>
@@ -2815,19 +2836,19 @@
       <c r="G42" s="8">
         <v>127</v>
       </c>
-      <c r="H42" s="13">
+      <c r="H42" s="14">
         <v>-12.6</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D43" s="16">
         <v>5268</v>
@@ -2841,19 +2862,19 @@
       <c r="G43" s="8">
         <v>95</v>
       </c>
-      <c r="H43" s="13">
+      <c r="H43" s="14">
         <v>-50.6</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D44" s="16">
         <v>10125</v>
@@ -2867,19 +2888,19 @@
       <c r="G44" s="8">
         <v>202</v>
       </c>
-      <c r="H44" s="13">
+      <c r="H44" s="14">
         <v>47.1</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D45" s="16">
         <v>12217</v>
@@ -2893,19 +2914,19 @@
       <c r="G45" s="8">
         <v>72</v>
       </c>
-      <c r="H45" s="13">
+      <c r="H45" s="14">
         <v>-10.7</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D46" s="16">
         <v>13951</v>
@@ -2919,25 +2940,25 @@
       <c r="G46" s="8">
         <v>177</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="14">
         <v>24.7</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D47" s="16">
         <v>15800</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>62</v>
+      <c r="E47" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="F47" s="8">
         <v>1726650</v>
@@ -2945,19 +2966,19 @@
       <c r="G47" s="8">
         <v>109</v>
       </c>
-      <c r="H47" s="13">
+      <c r="H47" s="14">
         <v>27.8</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D48" s="16">
         <v>13802</v>
@@ -2971,19 +2992,19 @@
       <c r="G48" s="8">
         <v>112</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="14">
         <v>-9.5</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D49" s="16">
         <v>1488</v>
@@ -2997,19 +3018,19 @@
       <c r="G49" s="8">
         <v>400</v>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="14">
         <v>-14.5</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D50" s="16">
         <v>9445</v>
@@ -3023,19 +3044,19 @@
       <c r="G50" s="8">
         <v>318</v>
       </c>
-      <c r="H50" s="13">
+      <c r="H50" s="14">
         <v>67.59999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D51" s="16">
         <v>31764</v>
@@ -3049,19 +3070,19 @@
       <c r="G51" s="8">
         <v>128</v>
       </c>
-      <c r="H51" s="13">
+      <c r="H51" s="14">
         <v>23.6</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D52" s="16">
         <v>4250</v>
@@ -3075,19 +3096,19 @@
       <c r="G52" s="8">
         <v>297</v>
       </c>
-      <c r="H52" s="13">
+      <c r="H52" s="14">
         <v>9.4</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D53" s="16">
         <v>5250</v>
@@ -3101,19 +3122,19 @@
       <c r="G53" s="8">
         <v>240</v>
       </c>
-      <c r="H53" s="13">
+      <c r="H53" s="14">
         <v>-0.8</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D54" s="16">
         <v>6250</v>
@@ -3127,19 +3148,19 @@
       <c r="G54" s="8">
         <v>112</v>
       </c>
-      <c r="H54" s="13">
+      <c r="H54" s="14">
         <v>-49.2</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D55" s="16">
         <v>12300</v>
@@ -3153,19 +3174,19 @@
       <c r="G55" s="8">
         <v>142</v>
       </c>
-      <c r="H55" s="13">
+      <c r="H55" s="14">
         <v>-40.2</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D56" s="16">
         <v>3921</v>
@@ -3179,19 +3200,19 @@
       <c r="G56" s="8">
         <v>306</v>
       </c>
-      <c r="H56" s="13">
+      <c r="H56" s="14">
         <v>7.9</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D57" s="16">
         <v>1200</v>
@@ -3205,19 +3226,19 @@
       <c r="G57" s="8">
         <v>562</v>
       </c>
-      <c r="H57" s="13">
+      <c r="H57" s="14">
         <v>5.6</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D58" s="16">
         <v>1200</v>
@@ -3231,25 +3252,25 @@
       <c r="G58" s="8">
         <v>403</v>
       </c>
-      <c r="H58" s="13">
+      <c r="H58" s="14">
         <v>-24.4</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D59" s="16">
         <v>15756</v>
       </c>
-      <c r="E59" s="15" t="s">
-        <v>62</v>
+      <c r="E59" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="F59" s="8">
         <v>901000</v>
@@ -3257,19 +3278,19 @@
       <c r="G59" s="8">
         <v>57</v>
       </c>
-      <c r="H59" s="13">
+      <c r="H59" s="14">
         <v>-48.3</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D60" s="16">
         <v>10125</v>
@@ -3283,19 +3304,19 @@
       <c r="G60" s="8">
         <v>372</v>
       </c>
-      <c r="H60" s="13">
+      <c r="H60" s="14">
         <v>103.4</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D61" s="16">
         <v>6997</v>
@@ -3309,19 +3330,19 @@
       <c r="G61" s="8">
         <v>457</v>
       </c>
-      <c r="H61" s="13">
+      <c r="H61" s="14">
         <v>98.59999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D62" s="16">
         <v>5625</v>
@@ -3335,19 +3356,19 @@
       <c r="G62" s="8">
         <v>284</v>
       </c>
-      <c r="H62" s="13">
+      <c r="H62" s="14">
         <v>69.40000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D63" s="16">
         <v>12496</v>
@@ -3361,19 +3382,19 @@
       <c r="G63" s="8">
         <v>76</v>
       </c>
-      <c r="H63" s="13">
+      <c r="H63" s="14">
         <v>-30.8</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D64" s="16">
         <v>7000</v>
@@ -3387,19 +3408,19 @@
       <c r="G64" s="8">
         <v>200</v>
       </c>
-      <c r="H64" s="13">
+      <c r="H64" s="14">
         <v>-2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D65" s="16">
         <v>1412</v>
@@ -3413,19 +3434,19 @@
       <c r="G65" s="8">
         <v>698</v>
       </c>
-      <c r="H65" s="13">
+      <c r="H65" s="14">
         <v>46.3</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D66" s="16">
         <v>1671</v>
@@ -3439,19 +3460,19 @@
       <c r="G66" s="8">
         <v>542</v>
       </c>
-      <c r="H66" s="13">
+      <c r="H66" s="14">
         <v>10.9</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D67" s="16">
         <v>6250</v>
@@ -3465,19 +3486,19 @@
       <c r="G67" s="8">
         <v>112</v>
       </c>
-      <c r="H67" s="13">
+      <c r="H67" s="14">
         <v>11.9</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D68" s="16">
         <v>6776</v>
@@ -3491,19 +3512,19 @@
       <c r="G68" s="8">
         <v>97</v>
       </c>
-      <c r="H68" s="13">
+      <c r="H68" s="14">
         <v>-53.1</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D69" s="16">
         <v>4633</v>
@@ -3517,19 +3538,19 @@
       <c r="G69" s="8">
         <v>130</v>
       </c>
-      <c r="H69" s="13">
+      <c r="H69" s="14">
         <v>-28.8</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D70" s="16">
         <v>7380</v>
@@ -3543,19 +3564,19 @@
       <c r="G70" s="8">
         <v>68</v>
       </c>
-      <c r="H70" s="13">
+      <c r="H70" s="14">
         <v>-25.6</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D71" s="16">
         <v>31542</v>
@@ -3569,19 +3590,19 @@
       <c r="G71" s="8">
         <v>109</v>
       </c>
-      <c r="H71" s="13">
+      <c r="H71" s="14">
         <v>-19.7</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D72" s="16">
         <v>13500</v>
@@ -3595,19 +3616,19 @@
       <c r="G72" s="8">
         <v>144</v>
       </c>
-      <c r="H72" s="13">
+      <c r="H72" s="14">
         <v>-30.3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D73" s="16">
         <v>5170</v>
@@ -3621,7 +3642,7 @@
       <c r="G73" s="8">
         <v>334</v>
       </c>
-      <c r="H73" s="13">
+      <c r="H73" s="14">
         <v>10.4</v>
       </c>
     </row>
@@ -3647,12 +3668,12 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3663,23 +3684,23 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="19" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B4" s="19"/>
       <c r="D4" s="19" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B5" s="20">
         <v>1800000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E5" s="21">
         <f>($B$6*$B$8*(1-$B$9))</f>
@@ -3688,13 +3709,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B6" s="22">
         <v>13402</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E6" s="23">
         <f>E5*(1-$B$10)</f>
@@ -3703,11 +3724,11 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="19" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B7" s="19"/>
       <c r="D7" s="5" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E7" s="12">
         <f>E6/$B$5</f>
@@ -3716,13 +3737,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B8" s="20">
         <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E8" s="23">
         <f>E6/$B$11</f>
@@ -3731,13 +3752,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B9" s="24">
         <v>0.06</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E9" s="12">
         <f>$B$14+$B$16/10000</f>
@@ -3746,13 +3767,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B10" s="24">
         <v>0.42</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E10" s="21">
         <f>$B$5*$B$13</f>
@@ -3761,13 +3782,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B11" s="25">
         <v>0.055</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E11" s="23">
         <f>$B$5*(1-$B$13)+$B$5*$B$23</f>
@@ -3776,11 +3797,11 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B12" s="19"/>
       <c r="D12" s="5" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E12" s="21">
         <f>E10*(E9/12)/(1-(1+E9/12)^-($B$15*12))*12</f>
@@ -3789,13 +3810,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="7" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B13" s="24">
         <v>0.6</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E13" s="26">
         <f>E6/E12</f>
@@ -3804,13 +3825,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B14" s="25">
         <v>0.0675</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="E14" s="27">
         <f>E6/E10</f>
@@ -3819,13 +3840,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="7" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B15" s="22">
         <v>25</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E15" s="27">
         <f>(D29-E12)/E11</f>
@@ -3834,13 +3855,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="7" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B16" s="28">
         <v>0</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E16" s="21">
         <f>($B$6*$B$8*(1-$B$9))*(1+$B$19)^$B$21-(($B$6*$B$8*(1-$B$9))*$B$10)*(1+$B$20)^$B$21</f>
@@ -3849,11 +3870,11 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="19" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B17" s="19"/>
       <c r="D17" s="5" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E17" s="23">
         <f>E16/$B$18</f>
@@ -3862,13 +3883,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="7" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B18" s="25">
         <v>0.0575</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E18" s="21">
         <f>E10*((1+E9/12)^($B$15*12)-(1+E9/12)^($B$21*12))/((1+E9/12)^($B$15*12)-1)</f>
@@ -3877,13 +3898,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="7" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B19" s="24">
         <v>0.03</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E19" s="23">
         <f>E17*(1-$B$22)-E18</f>
@@ -3892,13 +3913,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B20" s="24">
         <v>0.025</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E20" s="27">
         <f>IRR(G28:G38)</f>
@@ -3907,13 +3928,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B21" s="22">
         <v>5</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E21" s="26">
         <f>SUM(G29:G38)/E11</f>
@@ -3922,7 +3943,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="7" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B22" s="24">
         <v>0.02</v>
@@ -3930,7 +3951,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B23" s="24">
         <v>0.02</v>
@@ -3938,41 +3959,41 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="29">
         <v>0</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
       <c r="G28" s="21">
         <f>-E11</f>
         <v>-756000.0</v>
@@ -4270,21 +4291,21 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4505,19 +4526,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="8" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" customHeight="1">
+    <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -4529,7 +4551,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>32</v>
       </c>
@@ -4551,10 +4573,16 @@
       <c r="G4" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" s="8">
         <v>177</v>
@@ -4575,10 +4603,16 @@
         <f>C5*(1-D5)*(1-E5)/B5</f>
         <v>0.05544406779661017</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B6" s="8">
         <v>197</v>
@@ -4599,10 +4633,16 @@
         <f>C6*(1-D6)*(1-E6)/B6</f>
         <v>0.08068527918781726</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="8">
+        <v>17</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B7" s="8">
         <v>247</v>
@@ -4623,10 +4663,16 @@
         <f>C7*(1-D7)*(1-E7)/B7</f>
         <v>0.06682105263157895</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="8">
+        <v>28</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B8" s="8">
         <v>150</v>
@@ -4647,10 +4693,16 @@
         <f>C8*(1-D8)*(1-E8)/B8</f>
         <v>0.06459999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="8">
+        <v>19.4</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B9" s="8">
         <v>136</v>
@@ -4671,10 +4723,16 @@
         <f>C9*(1-D9)*(1-E9)/B9</f>
         <v>0.06882352941176471</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9" s="8">
+        <v>20.2</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B10" s="8">
         <v>347</v>
@@ -4695,10 +4753,16 @@
         <f>C10*(1-D10)*(1-E10)/B10</f>
         <v>0.07665706051873199</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B11" s="8">
         <v>365</v>
@@ -4719,10 +4783,16 @@
         <f>C11*(1-D11)*(1-E11)/B11</f>
         <v>0.06509589041095891</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="H11" s="8">
+        <v>22.6</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B12" s="8">
         <v>345</v>
@@ -4743,10 +4813,16 @@
         <f>C12*(1-D12)*(1-E12)/B12</f>
         <v>0.04266666666666667</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="H12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B13" s="8">
         <v>319</v>
@@ -4767,10 +4843,16 @@
         <f>C13*(1-D13)*(1-E13)/B13</f>
         <v>0.041034482758620684</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="H13" s="8">
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B14" s="8">
         <v>195</v>
@@ -4790,6 +4872,17 @@
       <c r="G14" s="12">
         <f>C14*(1-D14)*(1-E14)/B14</f>
         <v>0.0694974358974359</v>
+      </c>
+      <c r="H14" s="8">
+        <v>26.5</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4811,12 +4904,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4829,262 +4922,262 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B5" s="8">
         <v>268</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="14">
         <v>47.3</v>
       </c>
       <c r="D5" s="8">
         <v>1799000</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="14">
+        <v>46</v>
+      </c>
+      <c r="F5" s="15">
         <v>18</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="15">
         <v>63.6</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B6" s="8">
         <v>253</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <v>39.1</v>
       </c>
       <c r="D6" s="8">
         <v>3450000</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B7" s="8">
         <v>242</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="14">
         <v>33</v>
       </c>
       <c r="D7" s="8">
         <v>2100500</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="14">
+        <v>54</v>
+      </c>
+      <c r="F7" s="15">
         <v>18</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="15">
         <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B8" s="8">
         <v>186</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <v>2.2</v>
       </c>
       <c r="D8" s="8">
         <v>1700000</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="14">
+        <v>41</v>
+      </c>
+      <c r="F8" s="15">
         <v>8.199999999999999</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <v>68.59999999999999</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B9" s="8">
         <v>173</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>-4.9</v>
       </c>
       <c r="D9" s="8">
         <v>1328750</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="14">
+        <v>54</v>
+      </c>
+      <c r="F9" s="15">
         <v>4.5</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <v>55.6</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B10" s="8">
         <v>170</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <v>-6.5</v>
       </c>
       <c r="D10" s="8">
         <v>1074500</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="14">
+        <v>54</v>
+      </c>
+      <c r="F10" s="15">
         <v>28.3</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <v>74.09999999999999</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8">
         <v>153</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <v>-15.9</v>
       </c>
       <c r="D11" s="8">
         <v>1895000</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="14">
+        <v>41</v>
+      </c>
+      <c r="F11" s="15">
         <v>22.5</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <v>75</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B12" s="8">
         <v>126</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <v>-30.7</v>
       </c>
       <c r="D12" s="8">
         <v>1400000</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B13" s="8">
         <v>99</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="14">
         <v>-45.6</v>
       </c>
       <c r="D13" s="8">
         <v>732500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="14">
+        <v>54</v>
+      </c>
+      <c r="F13" s="15">
         <v>4.5</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <v>63.6</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5097,21 +5190,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="30" customHeight="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5122,322 +5215,388 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="8">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="8">
         <v>177</v>
       </c>
-      <c r="C5" s="16">
+      <c r="D5" s="16">
         <v>90</v>
       </c>
-      <c r="D5" s="16">
+      <c r="E5" s="16">
         <v>21</v>
       </c>
-      <c r="E5" s="8">
+      <c r="F5" s="8">
         <v>18</v>
       </c>
-      <c r="F5" s="17">
+      <c r="G5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="17">
         <v>0.06</v>
       </c>
-      <c r="G5" s="17">
+      <c r="I5" s="17">
         <v>0.42</v>
       </c>
-      <c r="H5" s="18">
+      <c r="J5" s="18">
         <v>0.055</v>
       </c>
-      <c r="I5" s="18">
+      <c r="K5" s="18">
         <v>0.0524</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="8">
+        <v>44</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="8">
         <v>197</v>
       </c>
-      <c r="C6" s="16">
+      <c r="D6" s="16">
         <v>29</v>
       </c>
-      <c r="D6" s="16">
+      <c r="E6" s="16">
         <v>3</v>
       </c>
-      <c r="E6" s="8">
+      <c r="F6" s="8">
         <v>34</v>
       </c>
-      <c r="F6" s="17">
+      <c r="G6" s="8">
+        <v>17</v>
+      </c>
+      <c r="H6" s="17">
         <v>0.15</v>
       </c>
-      <c r="G6" s="17">
+      <c r="I6" s="17">
         <v>0.45</v>
       </c>
-      <c r="H6" s="18">
+      <c r="J6" s="18">
         <v>0.08</v>
       </c>
-      <c r="I6" s="18">
+      <c r="K6" s="18">
         <v>0.0906</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:11">
       <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="8">
+        <v>46</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="8">
         <v>247</v>
       </c>
-      <c r="C7" s="16">
+      <c r="D7" s="16">
         <v>25</v>
       </c>
-      <c r="D7" s="16">
+      <c r="E7" s="16">
         <v>6</v>
       </c>
-      <c r="E7" s="8">
+      <c r="F7" s="8">
         <v>23</v>
       </c>
-      <c r="F7" s="17">
+      <c r="G7" s="8">
+        <v>28</v>
+      </c>
+      <c r="H7" s="17">
         <v>0.08</v>
       </c>
-      <c r="G7" s="17">
+      <c r="I7" s="17">
         <v>0.22</v>
       </c>
-      <c r="H7" s="18">
+      <c r="J7" s="18">
         <v>0.0675</v>
       </c>
-      <c r="I7" s="18">
+      <c r="K7" s="18">
         <v>0.0672</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="8">
+        <v>150</v>
+      </c>
+      <c r="D8" s="16">
+        <v>34</v>
+      </c>
+      <c r="E8" s="16">
+        <v>11</v>
+      </c>
+      <c r="F8" s="8">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8">
+        <v>19.4</v>
+      </c>
+      <c r="H8" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="I8" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="J8" s="18">
+        <v>0.0625</v>
+      </c>
+      <c r="K8" s="18">
+        <v>0.0658</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="8">
+        <v>136</v>
+      </c>
+      <c r="D9" s="16">
+        <v>33</v>
+      </c>
+      <c r="E9" s="16">
+        <v>5</v>
+      </c>
+      <c r="F9" s="8">
+        <v>16</v>
+      </c>
+      <c r="G9" s="8">
+        <v>20.2</v>
+      </c>
+      <c r="H9" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0.0675</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0.06859999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="8">
+        <v>347</v>
+      </c>
+      <c r="D10" s="16">
+        <v>11</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>100</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="8">
-        <v>150</v>
-      </c>
-      <c r="C8" s="16">
-        <v>34</v>
-      </c>
-      <c r="D8" s="16">
-        <v>11</v>
-      </c>
-      <c r="E8" s="8">
-        <v>12</v>
-      </c>
-      <c r="F8" s="17">
-        <v>0.05</v>
-      </c>
-      <c r="G8" s="17">
+      <c r="H10" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="17">
+        <v>0.62</v>
+      </c>
+      <c r="J10" s="18">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="K10" s="18">
+        <v>0.0665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="8">
+        <v>365</v>
+      </c>
+      <c r="D11" s="16">
+        <v>8</v>
+      </c>
+      <c r="E11" s="16">
+        <v>3</v>
+      </c>
+      <c r="F11" s="8">
+        <v>33</v>
+      </c>
+      <c r="G11" s="8">
+        <v>22.6</v>
+      </c>
+      <c r="H11" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0.065</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0.08210000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="8">
+        <v>345</v>
+      </c>
+      <c r="D12" s="16">
+        <v>3</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8">
+        <v>20</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="17">
+        <v>0.08</v>
+      </c>
+      <c r="I12" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K12" s="18">
+        <v>0.0427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="8">
+        <v>319</v>
+      </c>
+      <c r="D13" s="16">
+        <v>2</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>22</v>
+      </c>
+      <c r="G13" s="8">
+        <v>7.3</v>
+      </c>
+      <c r="H13" s="17">
         <v>0.15</v>
       </c>
-      <c r="H8" s="18">
-        <v>0.0625</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0.0658</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="4" t="s">
+      <c r="I13" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0.075</v>
+      </c>
+      <c r="K13" s="18">
+        <v>0.0522</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="8">
-        <v>136</v>
-      </c>
-      <c r="C9" s="16">
-        <v>33</v>
-      </c>
-      <c r="D9" s="16">
-        <v>5</v>
-      </c>
-      <c r="E9" s="8">
-        <v>16</v>
-      </c>
-      <c r="F9" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="17">
-        <v>0.35</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0.0675</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0.06859999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="8">
-        <v>347</v>
-      </c>
-      <c r="C10" s="16">
-        <v>11</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <v>100</v>
-      </c>
-      <c r="F10" s="17">
+      <c r="C14" s="8">
+        <v>195</v>
+      </c>
+      <c r="D14" s="16">
+        <v>96</v>
+      </c>
+      <c r="E14" s="16">
+        <v>20</v>
+      </c>
+      <c r="F14" s="8">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8">
+        <v>26.5</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0.12</v>
+      </c>
+      <c r="I14" s="17">
         <v>0.3</v>
       </c>
-      <c r="G10" s="17">
-        <v>0.62</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0.0665</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="8">
-        <v>365</v>
-      </c>
-      <c r="C11" s="16">
-        <v>8</v>
-      </c>
-      <c r="D11" s="16">
-        <v>3</v>
-      </c>
-      <c r="E11" s="8">
-        <v>33</v>
-      </c>
-      <c r="F11" s="17">
-        <v>0.1</v>
-      </c>
-      <c r="G11" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0.065</v>
-      </c>
-      <c r="I11" s="18">
-        <v>0.08210000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="8">
-        <v>345</v>
-      </c>
-      <c r="C12" s="16">
-        <v>3</v>
-      </c>
-      <c r="D12" s="16">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8">
-        <v>20</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0.08</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0.2</v>
-      </c>
-      <c r="H12" s="18">
+      <c r="J14" s="18">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I12" s="18">
-        <v>0.0427</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="8">
-        <v>319</v>
-      </c>
-      <c r="C13" s="16">
-        <v>2</v>
-      </c>
-      <c r="D13" s="16">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <v>22</v>
-      </c>
-      <c r="F13" s="17">
-        <v>0.15</v>
-      </c>
-      <c r="G13" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0.075</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0.0522</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="8">
-        <v>195</v>
-      </c>
-      <c r="C14" s="16">
-        <v>96</v>
-      </c>
-      <c r="D14" s="16">
-        <v>20</v>
-      </c>
-      <c r="E14" s="8">
-        <v>22</v>
-      </c>
-      <c r="F14" s="17">
-        <v>0.12</v>
-      </c>
-      <c r="G14" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="H14" s="18">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I14" s="18">
+      <c r="K14" s="18">
         <v>0.0644</v>
       </c>
     </row>
@@ -5460,12 +5619,12 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5481,48 +5640,48 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="I4" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" s="8">
         <v>320000</v>
@@ -5530,7 +5689,7 @@
       <c r="E5" s="8">
         <v>24</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <v>-76.7</v>
       </c>
       <c r="G5" s="18">
@@ -5542,22 +5701,22 @@
       <c r="I5" s="8">
         <v>2635192</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <v>-87.90000000000001</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D6" s="8">
         <v>2350000</v>
@@ -5565,7 +5724,7 @@
       <c r="E6" s="8">
         <v>84</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>-36.1</v>
       </c>
       <c r="G6" s="18">
@@ -5577,22 +5736,22 @@
       <c r="I6" s="8">
         <v>5397181</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <v>-56.5</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D7" s="8">
         <v>1995000</v>
@@ -5600,7 +5759,7 @@
       <c r="E7" s="8">
         <v>92</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <v>30.6</v>
       </c>
       <c r="G7" s="18">
@@ -5612,22 +5771,22 @@
       <c r="I7" s="8">
         <v>4329202</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="14">
         <v>-53.9</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D8" s="8">
         <v>1900000</v>
@@ -5635,7 +5794,7 @@
       <c r="E8" s="8">
         <v>92</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>-34.2</v>
       </c>
       <c r="G8" s="18">
@@ -5647,22 +5806,22 @@
       <c r="I8" s="8">
         <v>3990870</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <v>-52.4</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D9" s="8">
         <v>750000</v>
@@ -5670,7 +5829,7 @@
       <c r="E9" s="8">
         <v>120</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <v>-42.5</v>
       </c>
       <c r="G9" s="18">
@@ -5682,22 +5841,22 @@
       <c r="I9" s="8">
         <v>1527733</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="14">
         <v>-50.9</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D10" s="8">
         <v>799900</v>
@@ -5705,7 +5864,7 @@
       <c r="E10" s="8">
         <v>72</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <v>-58.9</v>
       </c>
       <c r="G10" s="18">
@@ -5717,22 +5876,22 @@
       <c r="I10" s="8">
         <v>1544192</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <v>-48.2</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="8">
         <v>1300000</v>
@@ -5740,7 +5899,7 @@
       <c r="E11" s="8">
         <v>94</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>-55.2</v>
       </c>
       <c r="G11" s="18">
@@ -5752,22 +5911,22 @@
       <c r="I11" s="8">
         <v>2462321</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <v>-47.2</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D12" s="8">
         <v>799000</v>
@@ -5775,7 +5934,7 @@
       <c r="E12" s="8">
         <v>117</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>-10</v>
       </c>
       <c r="G12" s="18">
@@ -5787,22 +5946,22 @@
       <c r="I12" s="8">
         <v>1359022</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="14">
         <v>-41.2</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D13" s="8">
         <v>1050000</v>
@@ -5810,7 +5969,7 @@
       <c r="E13" s="8">
         <v>156</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <v>-24.7</v>
       </c>
       <c r="G13" s="18">
@@ -5822,22 +5981,22 @@
       <c r="I13" s="8">
         <v>1650725</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <v>-36.4</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" s="8">
         <v>1050000</v>
@@ -5845,7 +6004,7 @@
       <c r="E14" s="8">
         <v>156</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <v>-24.7</v>
       </c>
       <c r="G14" s="18">
@@ -5857,22 +6016,22 @@
       <c r="I14" s="8">
         <v>1650725</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="14">
         <v>-36.4</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D15" s="8">
         <v>875000</v>
@@ -5880,7 +6039,7 @@
       <c r="E15" s="8">
         <v>128</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>-54.3</v>
       </c>
       <c r="G15" s="18">
@@ -5892,22 +6051,22 @@
       <c r="I15" s="8">
         <v>1324224</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="14">
         <v>-33.9</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D16" s="8">
         <v>1750000</v>
@@ -5915,7 +6074,7 @@
       <c r="E16" s="8">
         <v>104</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <v>-27</v>
       </c>
       <c r="G16" s="18">
@@ -5927,22 +6086,22 @@
       <c r="I16" s="8">
         <v>2616300</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="14">
         <v>-33.1</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" s="8">
         <v>1750000</v>
@@ -5950,7 +6109,7 @@
       <c r="E17" s="8">
         <v>122</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <v>-33.1</v>
       </c>
       <c r="G17" s="18">
@@ -5962,22 +6121,22 @@
       <c r="I17" s="8">
         <v>2551358</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="14">
         <v>-31.4</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D18" s="8">
         <v>2900000</v>
@@ -5985,7 +6144,7 @@
       <c r="E18" s="8">
         <v>135</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <v>-21.4</v>
       </c>
       <c r="G18" s="18">
@@ -5997,22 +6156,22 @@
       <c r="I18" s="8">
         <v>4152720</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="14">
         <v>-30.2</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D19" s="8">
         <v>7995000</v>
@@ -6020,7 +6179,7 @@
       <c r="E19" s="8">
         <v>220</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <v>12.4</v>
       </c>
       <c r="G19" s="18">
@@ -6032,22 +6191,22 @@
       <c r="I19" s="8">
         <v>11393249</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="14">
         <v>-29.8</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D20" s="8">
         <v>975000</v>
@@ -6055,7 +6214,7 @@
       <c r="E20" s="8">
         <v>139</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>-44</v>
       </c>
       <c r="G20" s="18">
@@ -6067,22 +6226,22 @@
       <c r="I20" s="8">
         <v>1355200</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="14">
         <v>-28.1</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D21" s="8">
         <v>1100000</v>
@@ -6090,7 +6249,7 @@
       <c r="E21" s="8">
         <v>100</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <v>-35.6</v>
       </c>
       <c r="G21" s="18">
@@ -6102,22 +6261,22 @@
       <c r="I21" s="8">
         <v>1518955</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="14">
         <v>-27.6</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D22" s="8">
         <v>1399990</v>
@@ -6125,7 +6284,7 @@
       <c r="E22" s="8">
         <v>138</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <v>-14.6</v>
       </c>
       <c r="G22" s="18">
@@ -6137,22 +6296,22 @@
       <c r="I22" s="8">
         <v>1806595</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="14">
         <v>-22.5</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D23" s="8">
         <v>975000</v>
@@ -6160,7 +6319,7 @@
       <c r="E23" s="8">
         <v>144</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <v>-64.40000000000001</v>
       </c>
       <c r="G23" s="18">
@@ -6172,22 +6331,22 @@
       <c r="I23" s="8">
         <v>1204396</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="14">
         <v>-19</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D24" s="8">
         <v>6000000</v>
@@ -6195,7 +6354,7 @@
       <c r="E24" s="8">
         <v>280</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <v>-25</v>
       </c>
       <c r="G24" s="18">
@@ -6207,22 +6366,22 @@
       <c r="I24" s="8">
         <v>6712588</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="14">
         <v>-10.6</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D25" s="8">
         <v>4250000</v>
@@ -6230,7 +6389,7 @@
       <c r="E25" s="8">
         <v>126</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <v>-7.1</v>
       </c>
       <c r="G25" s="18">
@@ -6242,22 +6401,22 @@
       <c r="I25" s="8">
         <v>4676256</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="14">
         <v>-9.1</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D26" s="8">
         <v>2940000</v>
@@ -6265,7 +6424,7 @@
       <c r="E26" s="8">
         <v>168</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <v>13.4</v>
       </c>
       <c r="G26" s="18">
@@ -6277,22 +6436,22 @@
       <c r="I26" s="8">
         <v>3122509</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="14">
         <v>-5.8</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D27" s="8">
         <v>2695000</v>
@@ -6300,7 +6459,7 @@
       <c r="E27" s="8">
         <v>192</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <v>0.5</v>
       </c>
       <c r="G27" s="18">
@@ -6312,22 +6471,22 @@
       <c r="I27" s="8">
         <v>2710400</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="14">
         <v>-0.6</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D28" s="8">
         <v>1150000</v>
@@ -6335,7 +6494,7 @@
       <c r="E28" s="8">
         <v>138</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <v>-23.5</v>
       </c>
       <c r="G28" s="18">
@@ -6347,22 +6506,22 @@
       <c r="I28" s="8">
         <v>1153013</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="14">
         <v>-0.3</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D29" s="8">
         <v>1999000</v>
@@ -6370,7 +6529,7 @@
       <c r="E29" s="8">
         <v>247</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <v>4.9</v>
       </c>
       <c r="G29" s="18">
@@ -6382,22 +6541,22 @@
       <c r="I29" s="8">
         <v>1982532</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="14">
         <v>0.8</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D30" s="8">
         <v>2399000</v>
@@ -6405,7 +6564,7 @@
       <c r="E30" s="8">
         <v>184</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <v>-32.4</v>
       </c>
       <c r="G30" s="18">
@@ -6417,22 +6576,22 @@
       <c r="I30" s="8">
         <v>2321541</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="14">
         <v>3.3</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D31" s="8">
         <v>2499999</v>
@@ -6440,7 +6599,7 @@
       <c r="E31" s="8">
         <v>185</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <v>-12.9</v>
       </c>
       <c r="G31" s="18">
@@ -6452,22 +6611,22 @@
       <c r="I31" s="8">
         <v>2410577</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="14">
         <v>3.7</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D32" s="8">
         <v>675000</v>
@@ -6475,7 +6634,7 @@
       <c r="E32" s="8">
         <v>144</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <v>-20.3</v>
       </c>
       <c r="G32" s="18">
@@ -6487,22 +6646,22 @@
       <c r="I32" s="8">
         <v>648960</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="14">
         <v>4</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D33" s="8">
         <v>1900000</v>
@@ -6510,7 +6669,7 @@
       <c r="E33" s="8">
         <v>188</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="14">
         <v>-42.6</v>
       </c>
       <c r="G33" s="18">
@@ -6522,22 +6681,22 @@
       <c r="I33" s="8">
         <v>1806773</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="14">
         <v>5.2</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D34" s="8">
         <v>3495000</v>
@@ -6545,7 +6704,7 @@
       <c r="E34" s="8">
         <v>168</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <v>-4.1</v>
       </c>
       <c r="G34" s="18">
@@ -6557,22 +6716,22 @@
       <c r="I34" s="8">
         <v>3229018</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="14">
         <v>8.199999999999999</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D35" s="8">
         <v>1999000</v>
@@ -6580,7 +6739,7 @@
       <c r="E35" s="8">
         <v>199</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <v>-20.1</v>
       </c>
       <c r="G35" s="18">
@@ -6592,22 +6751,22 @@
       <c r="I35" s="8">
         <v>1795175</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J35" s="14">
         <v>11.4</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D36" s="8">
         <v>3995000</v>
@@ -6615,7 +6774,7 @@
       <c r="E36" s="8">
         <v>197</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="14">
         <v>14.9</v>
       </c>
       <c r="G36" s="18">
@@ -6627,22 +6786,22 @@
       <c r="I36" s="8">
         <v>3534300</v>
       </c>
-      <c r="J36" s="13">
+      <c r="J36" s="14">
         <v>13</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D37" s="8">
         <v>10500000</v>
@@ -6650,7 +6809,7 @@
       <c r="E37" s="8">
         <v>219</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="14">
         <v>39.7</v>
       </c>
       <c r="G37" s="18">
@@ -6662,22 +6821,22 @@
       <c r="I37" s="8">
         <v>9283120</v>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="14">
         <v>13.1</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D38" s="8">
         <v>2100000</v>
@@ -6685,7 +6844,7 @@
       <c r="E38" s="8">
         <v>226</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <v>104.8</v>
       </c>
       <c r="G38" s="18">
@@ -6697,22 +6856,22 @@
       <c r="I38" s="8">
         <v>1845608</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="14">
         <v>13.8</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D39" s="8">
         <v>4000000</v>
@@ -6720,7 +6879,7 @@
       <c r="E39" s="8">
         <v>212</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="14">
         <v>18.9</v>
       </c>
       <c r="G39" s="18">
@@ -6732,22 +6891,22 @@
       <c r="I39" s="8">
         <v>3371953</v>
       </c>
-      <c r="J39" s="13">
+      <c r="J39" s="14">
         <v>18.6</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D40" s="8">
         <v>4000000</v>
@@ -6755,7 +6914,7 @@
       <c r="E40" s="8">
         <v>212</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="14">
         <v>18.9</v>
       </c>
       <c r="G40" s="18">
@@ -6767,22 +6926,22 @@
       <c r="I40" s="8">
         <v>3371953</v>
       </c>
-      <c r="J40" s="13">
+      <c r="J40" s="14">
         <v>18.6</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="4" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D41" s="8">
         <v>1749000</v>
@@ -6790,7 +6949,7 @@
       <c r="E41" s="8">
         <v>217</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="14">
         <v>-2.9</v>
       </c>
       <c r="G41" s="18">
@@ -6802,22 +6961,22 @@
       <c r="I41" s="8">
         <v>1440815</v>
       </c>
-      <c r="J41" s="13">
+      <c r="J41" s="14">
         <v>21.4</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="4" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D42" s="8">
         <v>2475000</v>
@@ -6825,7 +6984,7 @@
       <c r="E42" s="8">
         <v>238</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <v>-2.5</v>
       </c>
       <c r="G42" s="18">
@@ -6837,22 +6996,22 @@
       <c r="I42" s="8">
         <v>1855663</v>
       </c>
-      <c r="J42" s="13">
+      <c r="J42" s="14">
         <v>33.4</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D43" s="8">
         <v>1040000</v>
@@ -6860,7 +7019,7 @@
       <c r="E43" s="8">
         <v>200</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="14">
         <v>47.9</v>
       </c>
       <c r="G43" s="18">
@@ -6872,22 +7031,22 @@
       <c r="I43" s="8">
         <v>721067</v>
       </c>
-      <c r="J43" s="13">
+      <c r="J43" s="14">
         <v>44.2</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D44" s="8">
         <v>2100000</v>
@@ -6895,7 +7054,7 @@
       <c r="E44" s="8">
         <v>280</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <v>-6.8</v>
       </c>
       <c r="G44" s="18">
@@ -6907,22 +7066,22 @@
       <c r="I44" s="8">
         <v>1452581</v>
       </c>
-      <c r="J44" s="13">
+      <c r="J44" s="14">
         <v>44.6</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D45" s="8">
         <v>2500000</v>
@@ -6930,7 +7089,7 @@
       <c r="E45" s="8">
         <v>261</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="14">
         <v>15.4</v>
       </c>
       <c r="G45" s="18">
@@ -6942,22 +7101,22 @@
       <c r="I45" s="8">
         <v>1706853</v>
       </c>
-      <c r="J45" s="13">
+      <c r="J45" s="14">
         <v>46.5</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="4" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D46" s="8">
         <v>1999000</v>
@@ -6965,7 +7124,7 @@
       <c r="E46" s="8">
         <v>313</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <v>-23.9</v>
       </c>
       <c r="G46" s="18">
@@ -6977,22 +7136,22 @@
       <c r="I46" s="8">
         <v>1341202</v>
       </c>
-      <c r="J46" s="13">
+      <c r="J46" s="14">
         <v>49</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="4" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D47" s="8">
         <v>4900000</v>
@@ -7000,7 +7159,7 @@
       <c r="E47" s="8">
         <v>302</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <v>20.5</v>
       </c>
       <c r="G47" s="18">
@@ -7012,22 +7171,22 @@
       <c r="I47" s="8">
         <v>3146000</v>
       </c>
-      <c r="J47" s="13">
+      <c r="J47" s="14">
         <v>55.8</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D48" s="8">
         <v>710000</v>
@@ -7035,7 +7194,7 @@
       <c r="E48" s="8">
         <v>387</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <v>-6.2</v>
       </c>
       <c r="G48" s="18">
@@ -7047,22 +7206,22 @@
       <c r="I48" s="8">
         <v>448197</v>
       </c>
-      <c r="J48" s="13">
+      <c r="J48" s="14">
         <v>58.4</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="4" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D49" s="8">
         <v>1799000</v>
@@ -7070,7 +7229,7 @@
       <c r="E49" s="8">
         <v>257</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <v>-7.2</v>
       </c>
       <c r="G49" s="18">
@@ -7082,22 +7241,22 @@
       <c r="I49" s="8">
         <v>1085280</v>
       </c>
-      <c r="J49" s="13">
+      <c r="J49" s="14">
         <v>65.8</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="4" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D50" s="8">
         <v>2800000</v>
@@ -7105,7 +7264,7 @@
       <c r="E50" s="8">
         <v>238</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="14">
         <v>44.9</v>
       </c>
       <c r="G50" s="18">
@@ -7117,22 +7276,22 @@
       <c r="I50" s="8">
         <v>1630859</v>
       </c>
-      <c r="J50" s="13">
+      <c r="J50" s="14">
         <v>71.7</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D51" s="8">
         <v>2149000</v>
@@ -7140,7 +7299,7 @@
       <c r="E51" s="8">
         <v>324</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="14">
         <v>4.4</v>
       </c>
       <c r="G51" s="18">
@@ -7152,22 +7311,22 @@
       <c r="I51" s="8">
         <v>1183520</v>
       </c>
-      <c r="J51" s="13">
+      <c r="J51" s="14">
         <v>81.59999999999999</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D52" s="8">
         <v>4900000</v>
@@ -7175,7 +7334,7 @@
       <c r="E52" s="8">
         <v>362</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <v>31.3</v>
       </c>
       <c r="G52" s="18">
@@ -7187,22 +7346,22 @@
       <c r="I52" s="8">
         <v>2618440</v>
       </c>
-      <c r="J52" s="13">
+      <c r="J52" s="14">
         <v>87.09999999999999</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D53" s="8">
         <v>990000</v>
@@ -7210,7 +7369,7 @@
       <c r="E53" s="8">
         <v>412</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <v>81.7</v>
       </c>
       <c r="G53" s="18">
@@ -7222,22 +7381,22 @@
       <c r="I53" s="8">
         <v>476850</v>
       </c>
-      <c r="J53" s="13">
+      <c r="J53" s="14">
         <v>107.6</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D54" s="8">
         <v>1900000</v>
@@ -7245,7 +7404,7 @@
       <c r="E54" s="8">
         <v>298</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <v>0.9</v>
       </c>
       <c r="G54" s="18">
@@ -7257,22 +7416,22 @@
       <c r="I54" s="8">
         <v>885387</v>
       </c>
-      <c r="J54" s="13">
+      <c r="J54" s="14">
         <v>114.6</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D55" s="8">
         <v>995000</v>
@@ -7280,7 +7439,7 @@
       <c r="E55" s="8">
         <v>829</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="14">
         <v>0.8</v>
       </c>
       <c r="G55" s="18">
@@ -7292,22 +7451,22 @@
       <c r="I55" s="8">
         <v>438646</v>
       </c>
-      <c r="J55" s="13">
+      <c r="J55" s="14">
         <v>126.8</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D56" s="8">
         <v>2299000</v>
@@ -7315,7 +7474,7 @@
       <c r="E56" s="8">
         <v>406</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <v>66.59999999999999</v>
       </c>
       <c r="G56" s="18">
@@ -7327,22 +7486,22 @@
       <c r="I56" s="8">
         <v>785408</v>
       </c>
-      <c r="J56" s="13">
+      <c r="J56" s="14">
         <v>192.7</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D57" s="8">
         <v>3749000</v>
@@ -7350,7 +7509,7 @@
       <c r="E57" s="8">
         <v>555</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <v>36.2</v>
       </c>
       <c r="G57" s="18">
@@ -7362,22 +7521,22 @@
       <c r="I57" s="8">
         <v>1204396</v>
       </c>
-      <c r="J57" s="13">
+      <c r="J57" s="14">
         <v>211.3</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D58" s="8">
         <v>6000000</v>
@@ -7385,7 +7544,7 @@
       <c r="E58" s="8">
         <v>738</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="14">
         <v>94.59999999999999</v>
       </c>
       <c r="G58" s="18">
@@ -7397,22 +7556,22 @@
       <c r="I58" s="8">
         <v>1573194</v>
       </c>
-      <c r="J58" s="13">
+      <c r="J58" s="14">
         <v>281.4</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D59" s="8">
         <v>5000000</v>
@@ -7420,7 +7579,7 @@
       <c r="E59" s="8">
         <v>784</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="14">
         <v>81.59999999999999</v>
       </c>
       <c r="G59" s="18">
@@ -7432,22 +7591,22 @@
       <c r="I59" s="8">
         <v>1234200</v>
       </c>
-      <c r="J59" s="13">
+      <c r="J59" s="14">
         <v>305.1</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="4" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D60" s="8">
         <v>2400000</v>
@@ -7455,7 +7614,7 @@
       <c r="E60" s="8">
         <v>2166</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <v>160.7</v>
       </c>
       <c r="G60" s="18">
@@ -7467,11 +7626,11 @@
       <c r="I60" s="8">
         <v>214509</v>
       </c>
-      <c r="J60" s="13">
+      <c r="J60" s="14">
         <v>1018.8</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -7494,12 +7653,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7511,36 +7670,36 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D5" s="8">
         <v>2350000</v>
@@ -7548,22 +7707,22 @@
       <c r="E5" s="8">
         <v>5397181</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <v>-56.5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" s="8">
         <v>1995000</v>
@@ -7571,22 +7730,22 @@
       <c r="E6" s="8">
         <v>4329202</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>-53.9</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D7" s="8">
         <v>1900000</v>
@@ -7594,22 +7753,22 @@
       <c r="E7" s="8">
         <v>3990870</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <v>-52.4</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8" s="8">
         <v>750000</v>
@@ -7617,22 +7776,22 @@
       <c r="E8" s="8">
         <v>1527733</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>-50.9</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D9" s="8">
         <v>799900</v>
@@ -7640,22 +7799,22 @@
       <c r="E9" s="8">
         <v>1544192</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <v>-48.2</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8">
         <v>1300000</v>
@@ -7663,22 +7822,22 @@
       <c r="E10" s="8">
         <v>2462321</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <v>-47.2</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11" s="8">
         <v>799000</v>
@@ -7686,22 +7845,22 @@
       <c r="E11" s="8">
         <v>1359022</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>-41.2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D12" s="8">
         <v>1050000</v>
@@ -7709,22 +7868,22 @@
       <c r="E12" s="8">
         <v>1650725</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>-36.4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D13" s="8">
         <v>1050000</v>
@@ -7732,22 +7891,22 @@
       <c r="E13" s="8">
         <v>1650725</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <v>-36.4</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D14" s="8">
         <v>875000</v>
@@ -7755,22 +7914,22 @@
       <c r="E14" s="8">
         <v>1324224</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <v>-33.9</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D15" s="8">
         <v>1750000</v>
@@ -7778,22 +7937,22 @@
       <c r="E15" s="8">
         <v>2616300</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>-33.1</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" s="8">
         <v>1750000</v>
@@ -7801,22 +7960,22 @@
       <c r="E16" s="8">
         <v>2551358</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <v>-31.4</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D17" s="8">
         <v>2900000</v>
@@ -7824,22 +7983,22 @@
       <c r="E17" s="8">
         <v>4152720</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <v>-30.2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D18" s="8">
         <v>7995000</v>
@@ -7847,22 +8006,22 @@
       <c r="E18" s="8">
         <v>11393249</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <v>-29.8</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D19" s="8">
         <v>975000</v>
@@ -7870,22 +8029,22 @@
       <c r="E19" s="8">
         <v>1355200</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <v>-28.1</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D20" s="8">
         <v>1100000</v>
@@ -7893,22 +8052,22 @@
       <c r="E20" s="8">
         <v>1518955</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>-27.6</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D21" s="8">
         <v>1399990</v>
@@ -7916,22 +8075,22 @@
       <c r="E21" s="8">
         <v>1806595</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <v>-22.5</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D22" s="8">
         <v>975000</v>
@@ -7939,22 +8098,22 @@
       <c r="E22" s="8">
         <v>1204396</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <v>-19</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D23" s="8">
         <v>6000000</v>
@@ -7962,11 +8121,11 @@
       <c r="E23" s="8">
         <v>6712588</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <v>-10.6</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -7988,12 +8147,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8006,27 +8165,27 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B5" s="16">
         <v>96</v>
@@ -8040,13 +8199,13 @@
       <c r="E5" s="8">
         <v>194.5</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="15">
         <v>11.7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="16">
         <v>90</v>
@@ -8060,13 +8219,13 @@
       <c r="E6" s="8">
         <v>177.5</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <v>13.7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B7" s="16">
         <v>34</v>
@@ -8080,13 +8239,13 @@
       <c r="E7" s="8">
         <v>149.5</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <v>4.9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B8" s="16">
         <v>33</v>
@@ -8100,13 +8259,13 @@
       <c r="E8" s="8">
         <v>136</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <v>32.4</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B9" s="16">
         <v>29</v>
@@ -8120,13 +8279,13 @@
       <c r="E9" s="8">
         <v>197</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B10" s="16">
         <v>25</v>
@@ -8140,13 +8299,13 @@
       <c r="E10" s="8">
         <v>247</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="15">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B11" s="16">
         <v>11</v>
@@ -8160,13 +8319,13 @@
       <c r="E11" s="8">
         <v>347</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>62</v>
+      <c r="F11" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B12" s="16">
         <v>8</v>
@@ -8180,13 +8339,13 @@
       <c r="E12" s="8">
         <v>364.5</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="15">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B13" s="16">
         <v>3</v>
@@ -8200,13 +8359,13 @@
       <c r="E13" s="8">
         <v>345</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>62</v>
+      <c r="F13" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B14" s="16">
         <v>2</v>
@@ -8220,8 +8379,8 @@
       <c r="E14" s="8">
         <v>319</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>62</v>
+      <c r="F14" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8243,12 +8402,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8260,36 +8419,36 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5" s="8">
         <v>21000000</v>
@@ -8300,19 +8459,19 @@
       <c r="F5" s="8">
         <v>59</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="14">
         <v>842.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D6" s="8">
         <v>12500000</v>
@@ -8323,19 +8482,19 @@
       <c r="F6" s="8">
         <v>95</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <v>749.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D7" s="8">
         <v>7995000</v>
@@ -8346,19 +8505,19 @@
       <c r="F7" s="8">
         <v>77</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <v>730.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="8">
         <v>5200000</v>
@@ -8369,19 +8528,19 @@
       <c r="F8" s="8">
         <v>329</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <v>487.2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9" s="8">
         <v>23000000</v>
@@ -8392,19 +8551,19 @@
       <c r="F9" s="8">
         <v>148</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <v>448.6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8">
         <v>6895000</v>
@@ -8415,19 +8574,19 @@
       <c r="F10" s="8">
         <v>129</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <v>435.7</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D11" s="8">
         <v>11250000</v>
@@ -8438,19 +8597,19 @@
       <c r="F11" s="8">
         <v>139</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <v>371.2</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8">
         <v>12000000</v>
@@ -8461,19 +8620,19 @@
       <c r="F12" s="8">
         <v>515</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <v>272.8</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D13" s="8">
         <v>13900000</v>
@@ -8484,19 +8643,19 @@
       <c r="F13" s="8">
         <v>159</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <v>252.8</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" s="8">
         <v>7000000</v>
@@ -8507,19 +8666,19 @@
       <c r="F14" s="8">
         <v>127</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <v>226.9</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D15" s="8">
         <v>14750000</v>
@@ -8530,19 +8689,19 @@
       <c r="F15" s="8">
         <v>349</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <v>225.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D16" s="8">
         <v>14999000</v>
@@ -8553,19 +8712,19 @@
       <c r="F16" s="8">
         <v>342</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <v>225.4</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D17" s="8">
         <v>5000000</v>
@@ -8576,19 +8735,19 @@
       <c r="F17" s="8">
         <v>184</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <v>214.3</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D18" s="8">
         <v>8900000</v>
@@ -8599,19 +8758,19 @@
       <c r="F18" s="8">
         <v>110</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="14">
         <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19" s="8">
         <v>10795000</v>
@@ -8622,19 +8781,19 @@
       <c r="F19" s="8">
         <v>168</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="14">
         <v>201.8</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D20" s="8">
         <v>2200000</v>
@@ -8645,19 +8804,19 @@
       <c r="F20" s="8">
         <v>411</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="14">
         <v>189.2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D21" s="8">
         <v>5999999</v>
@@ -8668,19 +8827,19 @@
       <c r="F21" s="8">
         <v>63</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <v>184.6</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D22" s="8">
         <v>12400000</v>
@@ -8691,19 +8850,19 @@
       <c r="F22" s="8">
         <v>356</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="14">
         <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D23" s="8">
         <v>2043000</v>
@@ -8714,19 +8873,19 @@
       <c r="F23" s="8">
         <v>162</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <v>177.7</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D24" s="8">
         <v>2850000</v>
@@ -8737,19 +8896,19 @@
       <c r="F24" s="8">
         <v>140</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="14">
         <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25" s="8">
         <v>2800000</v>
@@ -8760,19 +8919,19 @@
       <c r="F25" s="8">
         <v>139</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="14">
         <v>167.7</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D26" s="8">
         <v>7600000</v>
@@ -8783,19 +8942,19 @@
       <c r="F26" s="8">
         <v>110</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="14">
         <v>159.6</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D27" s="8">
         <v>5000000</v>
@@ -8806,19 +8965,19 @@
       <c r="F27" s="8">
         <v>347</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="14">
         <v>151.8</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D28" s="8">
         <v>1740000</v>
@@ -8829,19 +8988,19 @@
       <c r="F28" s="8">
         <v>162</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="14">
         <v>136.5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D29" s="8">
         <v>1700000</v>
@@ -8852,19 +9011,19 @@
       <c r="F29" s="8">
         <v>166</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="14">
         <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D30" s="8">
         <v>7000000</v>
@@ -8875,19 +9034,19 @@
       <c r="F30" s="8">
         <v>177</v>
       </c>
-      <c r="G30" s="13">
+      <c r="G30" s="14">
         <v>134.4</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D31" s="8">
         <v>3500000</v>
@@ -8898,19 +9057,19 @@
       <c r="F31" s="8">
         <v>88</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <v>123.3</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D32" s="8">
         <v>2650000</v>
@@ -8921,19 +9080,19 @@
       <c r="F32" s="8">
         <v>152</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="14">
         <v>121.8</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D33" s="8">
         <v>2500000</v>
@@ -8944,19 +9103,19 @@
       <c r="F33" s="8">
         <v>633</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="14">
         <v>113.5</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="8">
         <v>7950000</v>
@@ -8967,19 +9126,19 @@
       <c r="F34" s="8">
         <v>97</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="14">
         <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D35" s="8">
         <v>1250000</v>
@@ -8990,19 +9149,19 @@
       <c r="F35" s="8">
         <v>192</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="14">
         <v>97.7</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D36" s="8">
         <v>6000000</v>
@@ -9013,19 +9172,19 @@
       <c r="F36" s="8">
         <v>380</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="14">
         <v>94.5</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D37" s="8">
         <v>1575000</v>
@@ -9036,19 +9195,19 @@
       <c r="F37" s="8">
         <v>216</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="14">
         <v>92.09999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D38" s="8">
         <v>4795000</v>
@@ -9059,19 +9218,19 @@
       <c r="F38" s="8">
         <v>250</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="14">
         <v>91.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D39" s="8">
         <v>1020000</v>
@@ -9082,19 +9241,19 @@
       <c r="F39" s="8">
         <v>227</v>
       </c>
-      <c r="G39" s="13">
+      <c r="G39" s="14">
         <v>87.2</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D40" s="8">
         <v>11900000</v>
@@ -9105,19 +9264,19 @@
       <c r="F40" s="8">
         <v>71</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="14">
         <v>85.8</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D41" s="8">
         <v>1000000</v>
@@ -9128,19 +9287,19 @@
       <c r="F41" s="8">
         <v>227</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="14">
         <v>83.59999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D42" s="8">
         <v>4490000</v>
@@ -9151,19 +9310,19 @@
       <c r="F42" s="8">
         <v>250</v>
       </c>
-      <c r="G42" s="13">
+      <c r="G42" s="14">
         <v>79.7</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="4" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D43" s="8">
         <v>4600000</v>
@@ -9174,19 +9333,19 @@
       <c r="F43" s="8">
         <v>202</v>
       </c>
-      <c r="G43" s="13">
+      <c r="G43" s="14">
         <v>79.40000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D44" s="8">
         <v>4500000</v>
@@ -9197,7 +9356,7 @@
       <c r="F44" s="8">
         <v>249</v>
       </c>
-      <c r="G44" s="13">
+      <c r="G44" s="14">
         <v>78.3</v>
       </c>
     </row>

--- a/commercial/outputs/Commercial_Deal_Dashboard.xlsx
+++ b/commercial/outputs/Commercial_Deal_Dashboard.xlsx
@@ -18,13 +18,14 @@
     <sheet name="Prospects" sheetId="9" r:id="rId9"/>
     <sheet name="Comps" sheetId="10" r:id="rId10"/>
     <sheet name="Scenario" sheetId="11" r:id="rId11"/>
+    <sheet name="Market" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="532">
   <si>
     <t>Commercial Deal Dashboard — Fort Lauderdale</t>
   </si>
@@ -92,6 +93,12 @@
     <t>Live underwriting — NOI built from assumptions.</t>
   </si>
   <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Researched benchmarks, costs &amp; the neighborhood playbook.</t>
+  </si>
+  <si>
     <t>Key conclusions</t>
   </si>
   <si>
@@ -1125,6 +1132,495 @@
   </si>
   <si>
     <t>Net proceeds</t>
+  </si>
+  <si>
+    <t>Market context — researched benchmarks</t>
+  </si>
+  <si>
+    <t>External Broward / Fort Lauderdale benchmarks, 2024–2025 (some Q1 2026); curated 2026-07-29. The market backdrop to compare your data against — verify before quoting a specific deal.</t>
+  </si>
+  <si>
+    <t>Benchmarks by asset class</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>Sale $/SF</t>
+  </si>
+  <si>
+    <t>Vacancy</t>
+  </si>
+  <si>
+    <t>Trend</t>
+  </si>
+  <si>
+    <t>4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%</t>
+  </si>
+  <si>
+    <t>priced per unit; ~$359,437/unit avg (2025 YTD)</t>
+  </si>
+  <si>
+    <t>~$300–450/SF on value-add product; per-unit is the metric</t>
+  </si>
+  <si>
+    <t>~7.9% (buildings 50+ units, Q3 2025)</t>
+  </si>
+  <si>
+    <t>Ranked #1 of 30 US markets for MF investment profitability; ~$1.8B annual volume; A/B cap compression, C softer. Live Local Act driving density.</t>
+  </si>
+  <si>
+    <t>~6.75–8.0%</t>
+  </si>
+  <si>
+    <t>$41.60/SF full-service overall (record high); Class A $46.74/SF; medical ~$34–36/SF</t>
+  </si>
+  <si>
+    <t>closed $196–442/SF (Plantation Place ~$196; Las Olas Centre trophy $442)</t>
+  </si>
+  <si>
+    <t>~12.3% (Broward, Q4 2025)</t>
+  </si>
+  <si>
+    <t>Flight-to-quality — post-2010 buildings hold occupancy while the market runs negative absorption; record asking rents; medical/healthcare growing.</t>
+  </si>
+  <si>
+    <t>~6.0–6.1%</t>
+  </si>
+  <si>
+    <t>$27.59/SF NNN Broward; Fort Lauderdale ~$36/SF; prime Las Olas/Downtown $50–75/SF</t>
+  </si>
+  <si>
+    <t>closed ~$391/SF (RK Centers, Riverbend, Dec 2025); listings avg ~$630/SF</t>
+  </si>
+  <si>
+    <t>~3.8–3.9% (very tight)</t>
+  </si>
+  <si>
+    <t>Sub-4% vacancy, little new supply, grocery-anchored &amp; infill centers in demand; absorption limited by scarce space, not weak demand.</t>
+  </si>
+  <si>
+    <t>~6.0–6.3% (South FL)</t>
+  </si>
+  <si>
+    <t>~$16/SF NNN (Fort Lauderdale ~$16.22); small-bay/flex $18–30/SF NNN</t>
+  </si>
+  <si>
+    <t>~$150–300/SF (well-located Broward warehouse)</t>
+  </si>
+  <si>
+    <t>~4.0–5.5% (rising on new supply)</t>
+  </si>
+  <si>
+    <t>Record pipeline concentrated in Pompano; small-bay/flex tight while big-box distribution absorbs slowly.</t>
+  </si>
+  <si>
+    <t>~7.8%</t>
+  </si>
+  <si>
+    <t>ADR $129 (summer trough) to ~$240 peak; per key ~$273,831</t>
+  </si>
+  <si>
+    <t>priced per key (~$274K/key), not per SF</t>
+  </si>
+  <si>
+    <t>occupancy ~55% (summer) to 72–85% (peak/annual, destination-wide)</t>
+  </si>
+  <si>
+    <t>801-room Omni + Whitfield/Auberge underway; beachfront commands a clear ADR premium; tourism/TDT revenue near record.</t>
+  </si>
+  <si>
+    <t>~6.0–6.75% (blends retail/MF)</t>
+  </si>
+  <si>
+    <t>ground-floor retail $27–75/SF NNN + residential above</t>
+  </si>
+  <si>
+    <t>varies with the residential/retail split</t>
+  </si>
+  <si>
+    <t>tracks its retail (sub-4%) and MF (~8%) components</t>
+  </si>
+  <si>
+    <t>The dominant new-development format downtown (Live Local density bonuses).</t>
+  </si>
+  <si>
+    <t>Construction (hard $/SqFt)</t>
+  </si>
+  <si>
+    <t>Multifamily — garden / wood (1–3 story)</t>
+  </si>
+  <si>
+    <t>$170–200/SF</t>
+  </si>
+  <si>
+    <t>Multifamily — mid-rise podium (5-over-1)</t>
+  </si>
+  <si>
+    <t>$200–275/SF</t>
+  </si>
+  <si>
+    <t>Multifamily — high-rise (concrete tower)</t>
+  </si>
+  <si>
+    <t>$400–675/SF</t>
+  </si>
+  <si>
+    <t>$200–575/SF (Class A $350–575)</t>
+  </si>
+  <si>
+    <t>Retail / strip center</t>
+  </si>
+  <si>
+    <t>$245–415/SF (standalone store ~$180/SF)</t>
+  </si>
+  <si>
+    <t>Industrial / warehouse (tilt-up)</t>
+  </si>
+  <si>
+    <t>$156–234/SF</t>
+  </si>
+  <si>
+    <t>$150–250 economy · $250–400 midscale · $400–600+/SF luxury</t>
+  </si>
+  <si>
+    <t>Renovation / rehab</t>
+  </si>
+  <si>
+    <t>Multifamily — light reno (paint/floors/fixtures)</t>
+  </si>
+  <si>
+    <t>$15,000–25,000/unit</t>
+  </si>
+  <si>
+    <t>Multifamily — moderate (kitchen/bath/appliances)</t>
+  </si>
+  <si>
+    <t>$25,000–45,000/unit</t>
+  </si>
+  <si>
+    <t>Multifamily — heavy / gut (systems)</t>
+  </si>
+  <si>
+    <t>$45,000–65,000+/unit</t>
+  </si>
+  <si>
+    <t>Office tenant improvement (Miami)</t>
+  </si>
+  <si>
+    <t>~$122/SF (Class A $135–150 · Class B $90–120)</t>
+  </si>
+  <si>
+    <t>Retail tenant improvement</t>
+  </si>
+  <si>
+    <t>$40–300/SF (restaurant $200–500/SF)</t>
+  </si>
+  <si>
+    <t>Florida cost adders</t>
+  </si>
+  <si>
+    <t>Soft costs</t>
+  </si>
+  <si>
+    <t>15–30% of hard costs</t>
+  </si>
+  <si>
+    <t>HVHZ hurricane-code premium (Broward/Miami-Dade)</t>
+  </si>
+  <si>
+    <t>+10–15% of construction cost</t>
+  </si>
+  <si>
+    <t>Builders-risk insurance (during build)</t>
+  </si>
+  <si>
+    <t>1–5% of value; coastal within ~1 mi 2–3×</t>
+  </si>
+  <si>
+    <t>Impact fees (Miami-Dade example)</t>
+  </si>
+  <si>
+    <t>~$7,500/MF unit · ~$13/SF commercial</t>
+  </si>
+  <si>
+    <t>Cost escalation (2025)</t>
+  </si>
+  <si>
+    <t>~+4–5.5%/yr (Turner index; RLB Miami +4.7–5.5% YoY)</t>
+  </si>
+  <si>
+    <t>Land basis</t>
+  </si>
+  <si>
+    <t>Commercial land (small infill)</t>
+  </si>
+  <si>
+    <t>~$944/SF (avg parcel ~6,700 SF); ~$4.04M/acre</t>
+  </si>
+  <si>
+    <t>Downtown per-buildable-unit land</t>
+  </si>
+  <si>
+    <t>~$82,000/unit (200 W Broward, 381 units, 2024)</t>
+  </si>
+  <si>
+    <t>Near-downtown per-unit land</t>
+  </si>
+  <si>
+    <t>~$38,000/unit (2125 S Andrews 'The Era', 400 units, 2024)</t>
+  </si>
+  <si>
+    <t>Flagler Village per-unit land</t>
+  </si>
+  <si>
+    <t>~$43,650/unit (Advantis assemblage, 252 units)</t>
+  </si>
+  <si>
+    <t>Waterfront luxury per-unit land</t>
+  </si>
+  <si>
+    <t>~$420,000/unit (900 Intracoastal 'Sage', 44 units, 2024)</t>
+  </si>
+  <si>
+    <t>Flagler Village land $/SF</t>
+  </si>
+  <si>
+    <t>$126–267/land SF (2024 comps)</t>
+  </si>
+  <si>
+    <t>Stabilized MF (residual-land context)</t>
+  </si>
+  <si>
+    <t>2025 YTD $359,437/unit @ $268/SF, ~$2,760/unit rent, 91.7% occ</t>
+  </si>
+  <si>
+    <t>Waterfront &amp; dockage</t>
+  </si>
+  <si>
+    <t>Waterfront premium</t>
+  </si>
+  <si>
+    <t>direct/unobstructed water access sells ~30–50% above comparable dry-lot</t>
+  </si>
+  <si>
+    <t>Waterfront land</t>
+  </si>
+  <si>
+    <t>~$4.84M/acre vs ~$4.04M/acre general commercial</t>
+  </si>
+  <si>
+    <t>Deep-water value driver</t>
+  </si>
+  <si>
+    <t>6 ft+ at mean low tide (8–12 ft for large vessels), NO fixed bridges, point lots = top value</t>
+  </si>
+  <si>
+    <t>Pricing convention</t>
+  </si>
+  <si>
+    <t>per linear foot of frontage, adjusted for depth, bridge clearance, seawall/dock</t>
+  </si>
+  <si>
+    <t>Seawall cost</t>
+  </si>
+  <si>
+    <t>~$500–1,000/linear foot</t>
+  </si>
+  <si>
+    <t>Marina slip rental</t>
+  </si>
+  <si>
+    <t>~$25/ft/month</t>
+  </si>
+  <si>
+    <t>Marina land comp</t>
+  </si>
+  <si>
+    <t>Lauderdale Marine Center (~60 ac) $340M in 2021 ≈ $5.67M/acre</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>MF insurance (Fort Lauderdale)</t>
+  </si>
+  <si>
+    <t>~$1,430/unit/yr (+53% YoY, 2024)</t>
+  </si>
+  <si>
+    <t>FL MF trend</t>
+  </si>
+  <si>
+    <t>~$800 → ~$2,000/unit over two years (+150%)</t>
+  </si>
+  <si>
+    <t>Per SqFt</t>
+  </si>
+  <si>
+    <t>$0.50–3.00/SF/yr (condo towers ~$0.23–0.26/SF/month)</t>
+  </si>
+  <si>
+    <t>Effect on value</t>
+  </si>
+  <si>
+    <t>insurance ~7% of opex but ~17% of expense growth since 2019 → compresses NOI, expands caps; FL values −6.8%</t>
+  </si>
+  <si>
+    <t>Flood (NFIP)</t>
+  </si>
+  <si>
+    <t>avg ~$938/yr; Zone AE $300–500K property ~$1,500–3,500/yr; VE = coastal high-hazard; Broward maps updated Jul 2024</t>
+  </si>
+  <si>
+    <t>Incentives</t>
+  </si>
+  <si>
+    <t>Opportunity Zones</t>
+  </si>
+  <si>
+    <t>Broward 30 tracts / Fort Lauderdale 10 — prime: Flagler Village, 13th St/Progresso, Sistrunk</t>
+  </si>
+  <si>
+    <t>NPF-CRA</t>
+  </si>
+  <si>
+    <t>Northwest–Progresso–Flagler Heights CRA grant/incentive programs; plan amended 2025</t>
+  </si>
+  <si>
+    <t>Live Local Act (SB 102)</t>
+  </si>
+  <si>
+    <t>by-right MF on commercial/industrial if ≥40% units ≤120% AMI; density = highest in jurisdiction, height = highest within 1 mi; 75–100% property-tax exemption on affordable units</t>
+  </si>
+  <si>
+    <t>Neighborhood playbook</t>
+  </si>
+  <si>
+    <t>Area 3600 → 17th Street Causeway / Harbor Beach / SE</t>
+  </si>
+  <si>
+    <t>The marine &amp; yachting-services heart of the market — and increasingly a waterfront redevelopment target.  RECENT: The Quay (1515 SE 17th) — Related/BH/PEBB bought the ~7-acre waterfront marina/retail site for $48.5M (2024) and won approval for a 521-unit tower (40% workforce, Live Local). F3 Marina automated drystack completed.  PLAY: Waterfront/marina redevelopment; dockage value; Live Local density on the water.</t>
+  </si>
+  <si>
+    <t>Area 3810 → Sistrunk / Progresso / Northwest</t>
+  </si>
+  <si>
+    <t>A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  RECENT: The Aldridge &amp; The Laramore — ~$42M, 72-unit mixed-use with retail at 1204 Sistrunk. NPF-CRA plan runs to 2035 with construction/façade incentives.  PLAY: Low basis vs downtown; land assembly on the OZ + CRA-incentive angle; Flagler Village spillover.</t>
+  </si>
+  <si>
+    <t>Area 3380 → Wilton Manors</t>
+  </si>
+  <si>
+    <t>A walkable, affluent arts-and-entertainment node (Wilton Drive) drawing its first mid-rise projects.  RECENT: Stiles bought the Shoppes of Wilton Manors (78,600 SF) for $27.6M (Dec 2024), pursuing an 82-unit rezoning; Kaplan's Generation proposes ~190 units.  PLAY: Retail redevelopment; constrained supply; strong restaurant/retail demand.</t>
+  </si>
+  <si>
+    <t>Area 3370 → Oakland Park</t>
+  </si>
+  <si>
+    <t>One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  RECENT: Culinary Arts District (NE 12th Ave) restaurant/distillery corridor; new City Hall mixed-use (2025); 6-acre Horizon redevelopment of the old City Hall site.  PLAY: Infill mixed-use, older-industrial repositioning; CRA incentives; attractive basis.</t>
+  </si>
+  <si>
+    <t>Area 3500 → Downtown / Flagler Village</t>
+  </si>
+  <si>
+    <t>The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  RECENT: FAT Village — Hines/Urban Street ~$500M, ~600 units + the region's first mass-timber office, topping off 2025, delivery mid-2026. Gallery at Flagler Village (263 units) queued. Class A office asking low-$40s/SF.  PLAY: Development &amp; land assembly; Live Local density bonuses; office repositioning.</t>
+  </si>
+  <si>
+    <t>Area 3800 → Downtown / Flagler Village</t>
+  </si>
+  <si>
+    <t>Area 3470 → Las Olas</t>
+  </si>
+  <si>
+    <t>Broward's premier office / CBD address — law, finance and wealth-management tenancy.  RECENT: 2025 delivered the two largest office trades in a decade: Las Olas Centre I &amp; II $208M (~$442/SF, Bradford Allen) and Bank of America Plaza at 401 E Las Olas ~$220M (Lone Star/Highline/Square2).  PLAY: Trophy office, repositioning, ground-floor retail at $50–75/SF.</t>
+  </si>
+  <si>
+    <t>Area 3460 → Sistrunk / Progresso / Northwest</t>
+  </si>
+  <si>
+    <t>Area 3160 → Fort Lauderdale Beach</t>
+  </si>
+  <si>
+    <t>The barrier-island beach market — hospitality, beachfront retail and boutique commercial/condo, where waterfront and ocean views drive a clear premium.  RECENT: Hotel product trades ~$274K/key with a beachfront ADR premium; retail/mixed commercial along the A1A / Ocean Blvd corridor.  PLAY: Hospitality &amp; beachfront retail; premium land; tourism demand.</t>
+  </si>
+  <si>
+    <t>Sources</t>
+  </si>
+  <si>
+    <t>Multifamily — CBRE (Calum Weaver) Fort Lauderdale submarket report 2024–25</t>
+  </si>
+  <si>
+    <t>Fort Lauderdale #1 MF profitability (Yardi Matrix / MIAMI REALTORS, Oct 2025)</t>
+  </si>
+  <si>
+    <t>Office &amp; Retail — Colliers Broward Q4 2025</t>
+  </si>
+  <si>
+    <t>Retail — Colliers Broward Q4 2025</t>
+  </si>
+  <si>
+    <t>Office/Retail — Matthews Fort Lauderdale reports 2025</t>
+  </si>
+  <si>
+    <t>Las Olas Centre $442/SF sale (CRE-Sources, Feb 2025)</t>
+  </si>
+  <si>
+    <t>401 E Las Olas / BofA tower ~$220M (The Real Deal, Feb 2025)</t>
+  </si>
+  <si>
+    <t>The Quay waterfront $48.5M (Commercial Observer, 2024)</t>
+  </si>
+  <si>
+    <t>Industrial — CBRE Broward Q1 2025</t>
+  </si>
+  <si>
+    <t>Industrial — JLL Broward Q1 2025</t>
+  </si>
+  <si>
+    <t>Hotel — Matthews Fort Lauderdale Hospitality Q3 2025</t>
+  </si>
+  <si>
+    <t>Construction cost — RSMeans</t>
+  </si>
+  <si>
+    <t>Construction escalation — Turner Building Cost Index 2025</t>
+  </si>
+  <si>
+    <t>Construction escalation — RLB North America Q3 2025</t>
+  </si>
+  <si>
+    <t>Office/retail TI &amp; rehab — Terrapin CG / CommercialCafe 2024–26</t>
+  </si>
+  <si>
+    <t>HVHZ &amp; builders-risk — Bridgeway Insurance 2026</t>
+  </si>
+  <si>
+    <t>Land values — LandSearch Fort Lauderdale</t>
+  </si>
+  <si>
+    <t>Per-unit land — The Real Deal / bldup 2024</t>
+  </si>
+  <si>
+    <t>Waterfront pricing — Gilles Rais Fine Homes 2026</t>
+  </si>
+  <si>
+    <t>MF insurance — Matthews Florida Multifamily 2024–25</t>
+  </si>
+  <si>
+    <t>Flood insurance — Harbour Insurance / NerdWallet 2026</t>
+  </si>
+  <si>
+    <t>Opportunity Zones — Greater Fort Lauderdale Alliance</t>
+  </si>
+  <si>
+    <t>Live Local Act — Holland &amp; Knight 2023</t>
+  </si>
+  <si>
+    <t>Submarkets — Florida YIMBY / The Real Deal / SFBJ 2024–25</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1637,7 @@
     <numFmt numFmtId="170" formatCode="0.00&quot;×&quot;"/>
     <numFmt numFmtId="171" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1193,6 +1689,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF2F6F9F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1302,7 +1806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1387,6 +1891,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1681,7 +2186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -1777,6 +2282,14 @@
       </c>
       <c r="B13" s="4" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="22" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1794,6 +2307,7 @@
     <hyperlink ref="A11" location="'Prospects'!A1" display="Prospects"/>
     <hyperlink ref="A12" location="'Comps'!A1" display="Comps"/>
     <hyperlink ref="A13" location="'Scenario'!A1" display="Scenario"/>
+    <hyperlink ref="A14" location="'Market'!A1" display="Market"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1810,12 +2324,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1828,39 +2342,39 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="16">
         <v>1500</v>
@@ -1880,13 +2394,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="16">
         <v>13402</v>
@@ -1906,13 +2420,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" s="16">
         <v>12500</v>
@@ -1932,19 +2446,19 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" s="16">
         <v>1938</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" s="8">
         <v>325000</v>
@@ -1958,13 +2472,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" s="16">
         <v>5200</v>
@@ -1984,19 +2498,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10" s="16">
         <v>1938</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" s="8">
         <v>185000</v>
@@ -2010,13 +2524,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" s="16">
         <v>10289</v>
@@ -2036,13 +2550,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="16">
         <v>36491</v>
@@ -2062,13 +2576,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="16">
         <v>17001</v>
@@ -2088,13 +2602,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" s="16">
         <v>22496</v>
@@ -2114,13 +2628,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D15" s="16">
         <v>12960</v>
@@ -2140,13 +2654,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" s="16">
         <v>6750</v>
@@ -2166,13 +2680,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" s="16">
         <v>5500</v>
@@ -2192,13 +2706,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D18" s="16">
         <v>5500</v>
@@ -2218,13 +2732,13 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="16">
         <v>6192</v>
@@ -2244,13 +2758,13 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D20" s="16">
         <v>11349</v>
@@ -2270,13 +2784,13 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" s="16">
         <v>11736</v>
@@ -2296,13 +2810,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D22" s="16">
         <v>10000</v>
@@ -2322,13 +2836,13 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D23" s="16">
         <v>13683</v>
@@ -2348,13 +2862,13 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D24" s="16">
         <v>9998</v>
@@ -2374,13 +2888,13 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D25" s="16">
         <v>16500</v>
@@ -2400,13 +2914,13 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" s="16">
         <v>11662</v>
@@ -2426,13 +2940,13 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D27" s="16">
         <v>11662</v>
@@ -2452,13 +2966,13 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D28" s="16">
         <v>6003</v>
@@ -2478,13 +2992,13 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D29" s="16">
         <v>3429</v>
@@ -2504,13 +3018,13 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D30" s="16">
         <v>6110</v>
@@ -2530,13 +3044,13 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D31" s="16">
         <v>9828</v>
@@ -2556,13 +3070,13 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D32" s="16">
         <v>7004</v>
@@ -2582,13 +3096,13 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D33" s="16">
         <v>1258</v>
@@ -2608,13 +3122,13 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D34" s="16">
         <v>35087</v>
@@ -2634,13 +3148,13 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D35" s="16">
         <v>7960</v>
@@ -2660,13 +3174,13 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D36" s="16">
         <v>13512</v>
@@ -2686,13 +3200,13 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D37" s="16">
         <v>11480</v>
@@ -2712,13 +3226,13 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D38" s="16">
         <v>6752</v>
@@ -2738,13 +3252,13 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D39" s="16">
         <v>1276</v>
@@ -2764,13 +3278,13 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D40" s="16">
         <v>25024</v>
@@ -2790,13 +3304,13 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D41" s="16">
         <v>6250</v>
@@ -2816,13 +3330,13 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D42" s="16">
         <v>20250</v>
@@ -2842,13 +3356,13 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D43" s="16">
         <v>5268</v>
@@ -2868,13 +3382,13 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D44" s="16">
         <v>10125</v>
@@ -2894,13 +3408,13 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D45" s="16">
         <v>12217</v>
@@ -2920,13 +3434,13 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D46" s="16">
         <v>13951</v>
@@ -2946,19 +3460,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D47" s="16">
         <v>15800</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F47" s="8">
         <v>1726650</v>
@@ -2972,13 +3486,13 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D48" s="16">
         <v>13802</v>
@@ -2998,13 +3512,13 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D49" s="16">
         <v>1488</v>
@@ -3024,13 +3538,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D50" s="16">
         <v>9445</v>
@@ -3050,13 +3564,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D51" s="16">
         <v>31764</v>
@@ -3076,13 +3590,13 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D52" s="16">
         <v>4250</v>
@@ -3102,13 +3616,13 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D53" s="16">
         <v>5250</v>
@@ -3128,13 +3642,13 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D54" s="16">
         <v>6250</v>
@@ -3154,13 +3668,13 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D55" s="16">
         <v>12300</v>
@@ -3180,13 +3694,13 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D56" s="16">
         <v>3921</v>
@@ -3206,13 +3720,13 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D57" s="16">
         <v>1200</v>
@@ -3232,13 +3746,13 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D58" s="16">
         <v>1200</v>
@@ -3258,19 +3772,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D59" s="16">
         <v>15756</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F59" s="8">
         <v>901000</v>
@@ -3284,13 +3798,13 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D60" s="16">
         <v>10125</v>
@@ -3310,13 +3824,13 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D61" s="16">
         <v>6997</v>
@@ -3336,13 +3850,13 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D62" s="16">
         <v>5625</v>
@@ -3362,13 +3876,13 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D63" s="16">
         <v>12496</v>
@@ -3388,13 +3902,13 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D64" s="16">
         <v>7000</v>
@@ -3414,13 +3928,13 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D65" s="16">
         <v>1412</v>
@@ -3440,13 +3954,13 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D66" s="16">
         <v>1671</v>
@@ -3466,13 +3980,13 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D67" s="16">
         <v>6250</v>
@@ -3492,13 +4006,13 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D68" s="16">
         <v>6776</v>
@@ -3518,13 +4032,13 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D69" s="16">
         <v>4633</v>
@@ -3544,13 +4058,13 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D70" s="16">
         <v>7380</v>
@@ -3570,13 +4084,13 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D71" s="16">
         <v>31542</v>
@@ -3596,13 +4110,13 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D72" s="16">
         <v>13500</v>
@@ -3622,13 +4136,13 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D73" s="16">
         <v>5170</v>
@@ -3668,12 +4182,12 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3684,23 +4198,23 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B4" s="19"/>
       <c r="D4" s="19" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B5" s="20">
         <v>1800000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E5" s="21">
         <f>($B$6*$B$8*(1-$B$9))</f>
@@ -3709,13 +4223,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B6" s="22">
         <v>13402</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E6" s="23">
         <f>E5*(1-$B$10)</f>
@@ -3724,11 +4238,11 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B7" s="19"/>
       <c r="D7" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E7" s="12">
         <f>E6/$B$5</f>
@@ -3737,13 +4251,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B8" s="20">
         <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E8" s="23">
         <f>E6/$B$11</f>
@@ -3752,13 +4266,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B9" s="24">
         <v>0.06</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E9" s="12">
         <f>$B$14+$B$16/10000</f>
@@ -3767,13 +4281,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B10" s="24">
         <v>0.42</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E10" s="21">
         <f>$B$5*$B$13</f>
@@ -3782,13 +4296,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B11" s="25">
         <v>0.055</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E11" s="23">
         <f>$B$5*(1-$B$13)+$B$5*$B$23</f>
@@ -3797,11 +4311,11 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B12" s="19"/>
       <c r="D12" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E12" s="21">
         <f>E10*(E9/12)/(1-(1+E9/12)^-($B$15*12))*12</f>
@@ -3810,13 +4324,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B13" s="24">
         <v>0.6</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E13" s="26">
         <f>E6/E12</f>
@@ -3825,13 +4339,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B14" s="25">
         <v>0.0675</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E14" s="27">
         <f>E6/E10</f>
@@ -3840,13 +4354,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B15" s="22">
         <v>25</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E15" s="27">
         <f>(D29-E12)/E11</f>
@@ -3855,13 +4369,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B16" s="28">
         <v>0</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E16" s="21">
         <f>($B$6*$B$8*(1-$B$9))*(1+$B$19)^$B$21-(($B$6*$B$8*(1-$B$9))*$B$10)*(1+$B$20)^$B$21</f>
@@ -3870,11 +4384,11 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B17" s="19"/>
       <c r="D17" s="5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E17" s="23">
         <f>E16/$B$18</f>
@@ -3883,13 +4397,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B18" s="25">
         <v>0.0575</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E18" s="21">
         <f>E10*((1+E9/12)^($B$15*12)-(1+E9/12)^($B$21*12))/((1+E9/12)^($B$15*12)-1)</f>
@@ -3898,13 +4412,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B19" s="24">
         <v>0.03</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E19" s="23">
         <f>E17*(1-$B$22)-E18</f>
@@ -3913,13 +4427,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B20" s="24">
         <v>0.025</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E20" s="27">
         <f>IRR(G28:G38)</f>
@@ -3928,13 +4442,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B21" s="22">
         <v>5</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E21" s="26">
         <f>SUM(G29:G38)/E11</f>
@@ -3943,7 +4457,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B22" s="24">
         <v>0.02</v>
@@ -3951,7 +4465,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B23" s="24">
         <v>0.02</v>
@@ -3959,30 +4473,30 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4291,21 +4805,21 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4453,6 +4967,998 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="D4:E4"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="2" max="6" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="58" customHeight="1">
+      <c r="A67" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" ht="58" customHeight="1">
+      <c r="A68" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6" ht="58" customHeight="1">
+      <c r="A69" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" ht="58" customHeight="1">
+      <c r="A70" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6" ht="58" customHeight="1">
+      <c r="A71" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6" ht="58" customHeight="1">
+      <c r="A72" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6" ht="58" customHeight="1">
+      <c r="A73" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6" ht="58" customHeight="1">
+      <c r="A74" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6" ht="58" customHeight="1">
+      <c r="A75" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="32" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="32" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="32" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="32" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="32" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="32" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="32" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="32" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="32" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="32" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="32" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="32" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="32" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="32" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="32" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="32" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="32" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="32" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="32" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="32" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="32" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="32" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="32" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="32" t="s">
+        <v>531</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A78" r:id="rId1"/>
+    <hyperlink ref="A79" r:id="rId2"/>
+    <hyperlink ref="A80" r:id="rId3"/>
+    <hyperlink ref="A81" r:id="rId4"/>
+    <hyperlink ref="A82" r:id="rId5"/>
+    <hyperlink ref="A83" r:id="rId6"/>
+    <hyperlink ref="A84" r:id="rId7"/>
+    <hyperlink ref="A85" r:id="rId8"/>
+    <hyperlink ref="A86" r:id="rId9"/>
+    <hyperlink ref="A87" r:id="rId10"/>
+    <hyperlink ref="A88" r:id="rId11"/>
+    <hyperlink ref="A89" r:id="rId12"/>
+    <hyperlink ref="A90" r:id="rId13"/>
+    <hyperlink ref="A91" r:id="rId14"/>
+    <hyperlink ref="A92" r:id="rId15"/>
+    <hyperlink ref="A93" r:id="rId16"/>
+    <hyperlink ref="A94" r:id="rId17"/>
+    <hyperlink ref="A95" r:id="rId18"/>
+    <hyperlink ref="A96" r:id="rId19"/>
+    <hyperlink ref="A97" r:id="rId20"/>
+    <hyperlink ref="A98" r:id="rId21"/>
+    <hyperlink ref="A99" r:id="rId22"/>
+    <hyperlink ref="A100" r:id="rId23"/>
+    <hyperlink ref="A101" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4468,55 +5974,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4536,12 +6042,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4553,36 +6059,36 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8">
         <v>177</v>
@@ -4604,15 +6110,15 @@
         <v>0.05544406779661017</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" s="8">
         <v>197</v>
@@ -4637,12 +6143,12 @@
         <v>17</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" s="8">
         <v>247</v>
@@ -4667,12 +6173,12 @@
         <v>28</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="8">
         <v>150</v>
@@ -4697,12 +6203,12 @@
         <v>19.4</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="8">
         <v>136</v>
@@ -4727,12 +6233,12 @@
         <v>20.2</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" s="8">
         <v>347</v>
@@ -4754,15 +6260,15 @@
         <v>0.07665706051873199</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" s="8">
         <v>365</v>
@@ -4787,12 +6293,12 @@
         <v>22.6</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" s="8">
         <v>345</v>
@@ -4814,15 +6320,15 @@
         <v>0.04266666666666667</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8">
         <v>319</v>
@@ -4847,12 +6353,12 @@
         <v>7.3</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="8">
         <v>195</v>
@@ -4877,12 +6383,12 @@
         <v>26.5</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4904,12 +6410,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4922,33 +6428,33 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B5" s="8">
         <v>268</v>
@@ -4960,7 +6466,7 @@
         <v>1799000</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" s="15">
         <v>18</v>
@@ -4969,12 +6475,12 @@
         <v>63.6</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" s="8">
         <v>253</v>
@@ -4986,21 +6492,21 @@
         <v>3450000</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B7" s="8">
         <v>242</v>
@@ -5012,7 +6518,7 @@
         <v>2100500</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F7" s="15">
         <v>18</v>
@@ -5021,12 +6527,12 @@
         <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" s="8">
         <v>186</v>
@@ -5038,7 +6544,7 @@
         <v>1700000</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" s="15">
         <v>8.199999999999999</v>
@@ -5047,12 +6553,12 @@
         <v>68.59999999999999</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B9" s="8">
         <v>173</v>
@@ -5064,7 +6570,7 @@
         <v>1328750</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="15">
         <v>4.5</v>
@@ -5073,12 +6579,12 @@
         <v>55.6</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="8">
         <v>170</v>
@@ -5090,7 +6596,7 @@
         <v>1074500</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="15">
         <v>28.3</v>
@@ -5099,12 +6605,12 @@
         <v>74.09999999999999</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="8">
         <v>153</v>
@@ -5116,7 +6622,7 @@
         <v>1895000</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" s="15">
         <v>22.5</v>
@@ -5125,12 +6631,12 @@
         <v>75</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="8">
         <v>126</v>
@@ -5142,21 +6648,21 @@
         <v>1400000</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="8">
         <v>99</v>
@@ -5168,7 +6674,7 @@
         <v>732500</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F13" s="15">
         <v>4.5</v>
@@ -5177,7 +6683,7 @@
         <v>63.6</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -5199,12 +6705,12 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5217,45 +6723,45 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="8">
         <v>177</v>
@@ -5270,7 +6776,7 @@
         <v>18</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="17">
         <v>0.06</v>
@@ -5287,10 +6793,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6" s="8">
         <v>197</v>
@@ -5322,10 +6828,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7" s="8">
         <v>247</v>
@@ -5357,10 +6863,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" s="8">
         <v>150</v>
@@ -5392,10 +6898,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="C9" s="8">
         <v>136</v>
@@ -5427,10 +6933,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" s="8">
         <v>347</v>
@@ -5445,7 +6951,7 @@
         <v>100</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" s="17">
         <v>0.3</v>
@@ -5462,10 +6968,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="8">
         <v>365</v>
@@ -5497,10 +7003,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="8">
         <v>345</v>
@@ -5515,7 +7021,7 @@
         <v>20</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" s="17">
         <v>0.08</v>
@@ -5532,10 +7038,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" s="8">
         <v>319</v>
@@ -5567,10 +7073,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="8">
         <v>195</v>
@@ -5619,12 +7125,12 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5640,48 +7146,48 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="8">
         <v>320000</v>
@@ -5705,18 +7211,18 @@
         <v>-87.90000000000001</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6" s="8">
         <v>2350000</v>
@@ -5740,18 +7246,18 @@
         <v>-56.5</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" s="8">
         <v>1995000</v>
@@ -5775,18 +7281,18 @@
         <v>-53.9</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" s="8">
         <v>1900000</v>
@@ -5810,18 +7316,18 @@
         <v>-52.4</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" s="8">
         <v>750000</v>
@@ -5845,18 +7351,18 @@
         <v>-50.9</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="8">
         <v>799900</v>
@@ -5880,18 +7386,18 @@
         <v>-48.2</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" s="8">
         <v>1300000</v>
@@ -5915,18 +7421,18 @@
         <v>-47.2</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="8">
         <v>799000</v>
@@ -5950,18 +7456,18 @@
         <v>-41.2</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="8">
         <v>1050000</v>
@@ -5985,18 +7491,18 @@
         <v>-36.4</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" s="8">
         <v>1050000</v>
@@ -6020,18 +7526,18 @@
         <v>-36.4</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="8">
         <v>875000</v>
@@ -6055,18 +7561,18 @@
         <v>-33.9</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" s="8">
         <v>1750000</v>
@@ -6090,18 +7596,18 @@
         <v>-33.1</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" s="8">
         <v>1750000</v>
@@ -6125,18 +7631,18 @@
         <v>-31.4</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" s="8">
         <v>2900000</v>
@@ -6160,18 +7666,18 @@
         <v>-30.2</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D19" s="8">
         <v>7995000</v>
@@ -6195,18 +7701,18 @@
         <v>-29.8</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" s="8">
         <v>975000</v>
@@ -6230,18 +7736,18 @@
         <v>-28.1</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="8">
         <v>1100000</v>
@@ -6265,18 +7771,18 @@
         <v>-27.6</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D22" s="8">
         <v>1399990</v>
@@ -6300,18 +7806,18 @@
         <v>-22.5</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D23" s="8">
         <v>975000</v>
@@ -6335,18 +7841,18 @@
         <v>-19</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24" s="8">
         <v>6000000</v>
@@ -6370,18 +7876,18 @@
         <v>-10.6</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" s="8">
         <v>4250000</v>
@@ -6405,18 +7911,18 @@
         <v>-9.1</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" s="8">
         <v>2940000</v>
@@ -6440,18 +7946,18 @@
         <v>-5.8</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D27" s="8">
         <v>2695000</v>
@@ -6475,18 +7981,18 @@
         <v>-0.6</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D28" s="8">
         <v>1150000</v>
@@ -6510,18 +8016,18 @@
         <v>-0.3</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D29" s="8">
         <v>1999000</v>
@@ -6545,18 +8051,18 @@
         <v>0.8</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D30" s="8">
         <v>2399000</v>
@@ -6580,18 +8086,18 @@
         <v>3.3</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D31" s="8">
         <v>2499999</v>
@@ -6615,18 +8121,18 @@
         <v>3.7</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D32" s="8">
         <v>675000</v>
@@ -6650,18 +8156,18 @@
         <v>4</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D33" s="8">
         <v>1900000</v>
@@ -6685,18 +8191,18 @@
         <v>5.2</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D34" s="8">
         <v>3495000</v>
@@ -6720,18 +8226,18 @@
         <v>8.199999999999999</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D35" s="8">
         <v>1999000</v>
@@ -6755,18 +8261,18 @@
         <v>11.4</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D36" s="8">
         <v>3995000</v>
@@ -6790,18 +8296,18 @@
         <v>13</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D37" s="8">
         <v>10500000</v>
@@ -6825,18 +8331,18 @@
         <v>13.1</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D38" s="8">
         <v>2100000</v>
@@ -6860,18 +8366,18 @@
         <v>13.8</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D39" s="8">
         <v>4000000</v>
@@ -6895,18 +8401,18 @@
         <v>18.6</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D40" s="8">
         <v>4000000</v>
@@ -6930,18 +8436,18 @@
         <v>18.6</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D41" s="8">
         <v>1749000</v>
@@ -6965,18 +8471,18 @@
         <v>21.4</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D42" s="8">
         <v>2475000</v>
@@ -7000,18 +8506,18 @@
         <v>33.4</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D43" s="8">
         <v>1040000</v>
@@ -7035,18 +8541,18 @@
         <v>44.2</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D44" s="8">
         <v>2100000</v>
@@ -7070,18 +8576,18 @@
         <v>44.6</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D45" s="8">
         <v>2500000</v>
@@ -7105,18 +8611,18 @@
         <v>46.5</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D46" s="8">
         <v>1999000</v>
@@ -7140,18 +8646,18 @@
         <v>49</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D47" s="8">
         <v>4900000</v>
@@ -7175,18 +8681,18 @@
         <v>55.8</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D48" s="8">
         <v>710000</v>
@@ -7210,18 +8716,18 @@
         <v>58.4</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D49" s="8">
         <v>1799000</v>
@@ -7245,18 +8751,18 @@
         <v>65.8</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D50" s="8">
         <v>2800000</v>
@@ -7280,18 +8786,18 @@
         <v>71.7</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D51" s="8">
         <v>2149000</v>
@@ -7315,18 +8821,18 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D52" s="8">
         <v>4900000</v>
@@ -7350,18 +8856,18 @@
         <v>87.09999999999999</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D53" s="8">
         <v>990000</v>
@@ -7385,18 +8891,18 @@
         <v>107.6</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D54" s="8">
         <v>1900000</v>
@@ -7420,18 +8926,18 @@
         <v>114.6</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D55" s="8">
         <v>995000</v>
@@ -7455,18 +8961,18 @@
         <v>126.8</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D56" s="8">
         <v>2299000</v>
@@ -7490,18 +8996,18 @@
         <v>192.7</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D57" s="8">
         <v>3749000</v>
@@ -7525,18 +9031,18 @@
         <v>211.3</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D58" s="8">
         <v>6000000</v>
@@ -7560,18 +9066,18 @@
         <v>281.4</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D59" s="8">
         <v>5000000</v>
@@ -7595,18 +9101,18 @@
         <v>305.1</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D60" s="8">
         <v>2400000</v>
@@ -7630,7 +9136,7 @@
         <v>1018.8</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -7653,12 +9159,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7670,36 +9176,36 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" s="8">
         <v>2350000</v>
@@ -7711,18 +9217,18 @@
         <v>-56.5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="8">
         <v>1995000</v>
@@ -7734,18 +9240,18 @@
         <v>-53.9</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" s="8">
         <v>1900000</v>
@@ -7757,18 +9263,18 @@
         <v>-52.4</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="8">
         <v>750000</v>
@@ -7780,18 +9286,18 @@
         <v>-50.9</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="8">
         <v>799900</v>
@@ -7803,18 +9309,18 @@
         <v>-48.2</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="8">
         <v>1300000</v>
@@ -7826,18 +9332,18 @@
         <v>-47.2</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="8">
         <v>799000</v>
@@ -7849,18 +9355,18 @@
         <v>-41.2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="8">
         <v>1050000</v>
@@ -7872,18 +9378,18 @@
         <v>-36.4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D13" s="8">
         <v>1050000</v>
@@ -7895,18 +9401,18 @@
         <v>-36.4</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="8">
         <v>875000</v>
@@ -7918,18 +9424,18 @@
         <v>-33.9</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="8">
         <v>1750000</v>
@@ -7941,18 +9447,18 @@
         <v>-33.1</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" s="8">
         <v>1750000</v>
@@ -7964,18 +9470,18 @@
         <v>-31.4</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D17" s="8">
         <v>2900000</v>
@@ -7987,18 +9493,18 @@
         <v>-30.2</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="8">
         <v>7995000</v>
@@ -8010,18 +9516,18 @@
         <v>-29.8</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D19" s="8">
         <v>975000</v>
@@ -8033,18 +9539,18 @@
         <v>-28.1</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D20" s="8">
         <v>1100000</v>
@@ -8056,18 +9562,18 @@
         <v>-27.6</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D21" s="8">
         <v>1399990</v>
@@ -8079,18 +9585,18 @@
         <v>-22.5</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D22" s="8">
         <v>975000</v>
@@ -8102,18 +9608,18 @@
         <v>-19</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" s="8">
         <v>6000000</v>
@@ -8125,7 +9631,7 @@
         <v>-10.6</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -8147,12 +9653,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8165,27 +9671,27 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="16">
         <v>96</v>
@@ -8205,7 +9711,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="16">
         <v>90</v>
@@ -8225,7 +9731,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B7" s="16">
         <v>34</v>
@@ -8245,7 +9751,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="16">
         <v>33</v>
@@ -8265,7 +9771,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" s="16">
         <v>29</v>
@@ -8285,7 +9791,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="16">
         <v>25</v>
@@ -8305,7 +9811,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B11" s="16">
         <v>11</v>
@@ -8320,12 +9826,12 @@
         <v>347</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" s="16">
         <v>8</v>
@@ -8345,7 +9851,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B13" s="16">
         <v>3</v>
@@ -8360,12 +9866,12 @@
         <v>345</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" s="16">
         <v>2</v>
@@ -8380,7 +9886,7 @@
         <v>319</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -8402,12 +9908,12 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8419,36 +9925,36 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="8">
         <v>21000000</v>
@@ -8465,13 +9971,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="8">
         <v>12500000</v>
@@ -8488,13 +9994,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" s="8">
         <v>7995000</v>
@@ -8511,13 +10017,13 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8">
         <v>5200000</v>
@@ -8534,13 +10040,13 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" s="8">
         <v>23000000</v>
@@ -8557,13 +10063,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="8">
         <v>6895000</v>
@@ -8580,13 +10086,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" s="8">
         <v>11250000</v>
@@ -8603,13 +10109,13 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="8">
         <v>12000000</v>
@@ -8626,13 +10132,13 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="8">
         <v>13900000</v>
@@ -8649,13 +10155,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" s="8">
         <v>7000000</v>
@@ -8672,13 +10178,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="8">
         <v>14750000</v>
@@ -8695,13 +10201,13 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="8">
         <v>14999000</v>
@@ -8718,13 +10224,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="8">
         <v>5000000</v>
@@ -8741,13 +10247,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D18" s="8">
         <v>8900000</v>
@@ -8764,13 +10270,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19" s="8">
         <v>10795000</v>
@@ -8787,13 +10293,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D20" s="8">
         <v>2200000</v>
@@ -8810,13 +10316,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21" s="8">
         <v>5999999</v>
@@ -8833,13 +10339,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" s="8">
         <v>12400000</v>
@@ -8856,13 +10362,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D23" s="8">
         <v>2043000</v>
@@ -8879,13 +10385,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" s="8">
         <v>2850000</v>
@@ -8902,13 +10408,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D25" s="8">
         <v>2800000</v>
@@ -8925,13 +10431,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D26" s="8">
         <v>7600000</v>
@@ -8948,13 +10454,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D27" s="8">
         <v>5000000</v>
@@ -8971,13 +10477,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D28" s="8">
         <v>1740000</v>
@@ -8994,13 +10500,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D29" s="8">
         <v>1700000</v>
@@ -9017,13 +10523,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D30" s="8">
         <v>7000000</v>
@@ -9040,13 +10546,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D31" s="8">
         <v>3500000</v>
@@ -9063,13 +10569,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D32" s="8">
         <v>2650000</v>
@@ -9086,13 +10592,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D33" s="8">
         <v>2500000</v>
@@ -9109,13 +10615,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D34" s="8">
         <v>7950000</v>
@@ -9132,13 +10638,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D35" s="8">
         <v>1250000</v>
@@ -9155,13 +10661,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D36" s="8">
         <v>6000000</v>
@@ -9178,13 +10684,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D37" s="8">
         <v>1575000</v>
@@ -9201,13 +10707,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D38" s="8">
         <v>4795000</v>
@@ -9224,13 +10730,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="8">
         <v>1020000</v>
@@ -9247,13 +10753,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D40" s="8">
         <v>11900000</v>
@@ -9270,13 +10776,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D41" s="8">
         <v>1000000</v>
@@ -9293,13 +10799,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D42" s="8">
         <v>4490000</v>
@@ -9316,13 +10822,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D43" s="8">
         <v>4600000</v>
@@ -9339,13 +10845,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D44" s="8">
         <v>4500000</v>

--- a/commercial/outputs/Commercial_Deal_Dashboard.xlsx
+++ b/commercial/outputs/Commercial_Deal_Dashboard.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3968" uniqueCount="1400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3968" uniqueCount="1401">
   <si>
     <t>Commercial Deal Dashboard — Fort Lauderdale</t>
   </si>
@@ -328,10 +328,10 @@
     <t>From the MLS, export the properties as a CSV in the 'Agent Single Line — COM' layout (or any CSV with the columns below).</t>
   </si>
   <si>
-    <t>2. Replace the data</t>
-  </si>
-  <si>
-    <t>Put your CSV(s) in  commercial/data/raw/  and delete the old ones (the tool reads every CSV in that folder).</t>
+    <t>2. Add / replace the data</t>
+  </si>
+  <si>
+    <t>Put your CSV(s) in  commercial/data/raw/. To fully replace, delete the old files; to UPDATE OVER TIME just add the newer pull — the tool reads every CSV and, for any listing that appears in more than one, keeps the most-progressed status and the NEWEST pull.</t>
   </si>
   <si>
     <t>3. Run</t>
@@ -568,7 +568,7 @@
     <t>Cancelled</t>
   </si>
   <si>
-    <t>Hi, I saw 2000 S Federal Highway came off the market — I cover Federal Hwy · SE 17th St. Retail around here is trading near $127/SF and leasing around $28/SF. I think it can be positioned to actually sell — got two minutes?</t>
+    <t>Hi, I saw 2000 S Federal Highway came off the market — I cover Federal Hwy · SR-84. Retail around here is trading near $127/SF and leasing around $28/SF. I think it can be positioned to actually sell — got two minutes?</t>
   </si>
   <si>
     <t>Comps put it around $2.14M (~$127/SF) — about a 4.0% cap at market rents. It should rent ~$28/SF — about $472K/yr gross.</t>
@@ -688,6 +688,21 @@
     <t>What's it worth? Comps support ~$4.83M (~$241/SF). You were asking $5.29M.  •  What does it rent for? ~$15/SF/yr — about $308K/yr gross on 20,020 SF.  •  What cap? ~3.7% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? The marine &amp; yachting-services heart of the market — and increasingly a waterfront redevelopment target.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>511 SE 5th Ave Unit#101/102</t>
+  </si>
+  <si>
+    <t>Restaurant</t>
+  </si>
+  <si>
+    <t>Hi, I saw 511 SE 5th Ave Unit#101/102 came off the market — I cover Andrews Ave · SE 17th St. Restaurant/bar around here is trading near $184/SF and leasing around $23/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $1.59M (~$184/SF) — about a 4.1% cap at market rents. It should rent ~$23/SF — about $196K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$1.59M (~$184/SF). You were asking $5.00M.  •  What does it rent for? ~$23/SF/yr — about $196K/yr gross on 8,664 SF.  •  What cap? ~4.1% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>431 NW 1st Avenue</t>
   </si>
   <si>
@@ -703,21 +718,6 @@
     <t>What's it worth? Comps support ~$4.22M (~$265/SF). You were asking $5.00M.  •  What does it rent for? ~$26/SF/yr — about $422K/yr gross on 15,937 SF.  •  What cap? ~4.3% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>511 SE 5th Ave Unit#101/102</t>
-  </si>
-  <si>
-    <t>Restaurant</t>
-  </si>
-  <si>
-    <t>Hi, I saw 511 SE 5th Ave Unit#101/102 came off the market — I cover Andrews Ave · SE 17th St. Restaurant/bar around here is trading near $184/SF and leasing around $23/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $1.59M (~$184/SF) — about a 4.1% cap at market rents. It should rent ~$23/SF — about $196K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$1.59M (~$184/SF). You were asking $5.00M.  •  What does it rent for? ~$23/SF/yr — about $196K/yr gross on 8,664 SF.  •  What cap? ~4.1% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>1843 S Federal Highway</t>
   </si>
   <si>
@@ -745,6 +745,18 @@
     <t>What's it worth? Comps support ~$2.69M (~$59/SF). You were asking $4.50M.  •  What does it rent for? ~$26/SF/yr — about $1.21M/yr gross on 45,568 SF.  •  What cap? ~13.7% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? The barrier-island beach market — hospitality, beachfront retail and boutique commercial/condo, where waterfront and ocean views drive a clear premium.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>2817 E Oakland Park Boulevard</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2817 E Oakland Park Boulevard came off the market — I cover Oakland Park Blvd. Commercial around here is trading near $209/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $3.11M (~$209/SF) — about a 4.5% cap at market rents. It should rent ~$26/SF — about $394K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$3.11M (~$209/SF). You were asking $4.50M.  •  What does it rent for? ~$26/SF/yr — about $394K/yr gross on 14,860 SF.  •  What cap? ~4.5% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>2648 NE 32nd Street</t>
   </si>
   <si>
@@ -757,18 +769,6 @@
     <t>What's it worth? Comps support ~$5.54M (~$277/SF). You were asking $4.50M.  •  What cap? ~11.8% implied from lease-vs-sale comps (market benchmark ~7.8%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>2817 E Oakland Park Boulevard</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2817 E Oakland Park Boulevard came off the market — I cover Oakland Park Blvd. Commercial around here is trading near $209/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $3.11M (~$209/SF) — about a 4.5% cap at market rents. It should rent ~$26/SF — about $394K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$3.11M (~$209/SF). You were asking $4.50M.  •  What does it rent for? ~$26/SF/yr — about $394K/yr gross on 14,860 SF.  •  What cap? ~4.5% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>702-704 NE 1st Avenue</t>
   </si>
   <si>
@@ -868,6 +868,12 @@
     <t>What's it worth? Comps support ~$2.47M (~$100/SF). You were asking $3.65M.  •  What does it rent for? ~$28/SF/yr — about $692K/yr gross on 24,725 SF.  •  What cap? ~11.2% implied from lease-vs-sale comps (market benchmark ~6.0–6.1%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>Comps put it around $3.12M (~$208/SF) — about a 5.7% cap at market rents. It should rent ~$26/SF — about $398K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$3.12M (~$208/SF). You were asking $3.60M.  •  What does it rent for? ~$26/SF/yr — about $398K/yr gross on 15,000 SF.  •  What cap? ~5.7% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>2905 NE 6th Avenue</t>
   </si>
   <si>
@@ -880,12 +886,6 @@
     <t>What's it worth? Comps support ~$4.18M (~$139/SF). You were asking $3.60M.  •  What does it rent for? ~$26/SF/yr — about $797K/yr gross on 30,093 SF.  •  What cap? ~11.3% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>Comps put it around $3.12M (~$208/SF) — about a 5.7% cap at market rents. It should rent ~$26/SF — about $398K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$3.12M (~$208/SF). You were asking $3.60M.  •  What does it rent for? ~$26/SF/yr — about $398K/yr gross on 15,000 SF.  •  What cap? ~5.7% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>2120 S Federal Hwy</t>
   </si>
   <si>
@@ -1111,6 +1111,33 @@
     <t>What's it worth? Comps support ~$2.00M (~$320/SF). You were asking $2.75M.  •  What does it rent for? ~$15/SF/yr — about $96K/yr gross on 6,250 SF.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>2010 Wilton Dr</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2010 Wilton Dr came off the market — I cover Wilton Dr · Federal Hwy. Restaurant/bar around here is trading near $272/SF and leasing around $23/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.17M (~$272/SF) — about a 6.9% cap at market rents. It should rent ~$23/SF — about $180K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.17M (~$272/SF). You were asking $2.75M.  •  What does it rent for? ~$23/SF/yr — about $180K/yr gross on 7,960 SF.  •  What cap? ~6.9% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? A walkable, affluent arts-and-entertainment node (Wilton Drive) drawing its first mid-rise projects.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
+    <t>114 NW 25th Street</t>
+  </si>
+  <si>
+    <t>Area 3390</t>
+  </si>
+  <si>
+    <t>Hi, I saw 114 NW 25th Street came off the market — I cover Oakland Park Blvd · SE 17th St. Multifamily around here is trading near $119/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $4.78M (~$119/SF) — about a 14.3% cap at market rents. It should rent ~$15/SF — about $619K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$4.78M (~$119/SF). You were asking $2.75M.  •  What does it rent for? ~$15/SF/yr — about $619K/yr gross on 40,196 SF.  •  What cap? ~14.3% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>15 NW 9th Ave</t>
   </si>
   <si>
@@ -1123,33 +1150,6 @@
     <t>What's it worth? Comps support ~$1.94M (~$277/SF). You were asking $2.75M.  •  What does it rent for? ~$19/SF/yr — about $136K/yr gross on 7,000 SF.  •  How's demand? Broward's premier office / CBD address — law, finance and wealth-management tenancy.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>114 NW 25th Street</t>
-  </si>
-  <si>
-    <t>Area 3390</t>
-  </si>
-  <si>
-    <t>Hi, I saw 114 NW 25th Street came off the market — I cover Oakland Park Blvd · SE 17th St. Multifamily around here is trading near $119/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $4.78M (~$119/SF) — about a 14.3% cap at market rents. It should rent ~$15/SF — about $619K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$4.78M (~$119/SF). You were asking $2.75M.  •  What does it rent for? ~$15/SF/yr — about $619K/yr gross on 40,196 SF.  •  What cap? ~14.3% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>2010 Wilton Dr</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2010 Wilton Dr came off the market — I cover Wilton Dr · Federal Hwy. Restaurant/bar around here is trading near $272/SF and leasing around $23/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.17M (~$272/SF) — about a 6.9% cap at market rents. It should rent ~$23/SF — about $180K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.17M (~$272/SF). You were asking $2.75M.  •  What does it rent for? ~$23/SF/yr — about $180K/yr gross on 7,960 SF.  •  What cap? ~6.9% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? A walkable, affluent arts-and-entertainment node (Wilton Drive) drawing its first mid-rise projects.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>724-730 3rd Avenue</t>
   </si>
   <si>
@@ -1198,6 +1198,18 @@
     <t>What's it worth? Comps support ~$1.88M (~$601/SF). You were asking $2.50M.  •  What does it rent for? ~$26/SF/yr — about $83K/yr gross on 3,130 SF.  •  How's demand? A walkable, affluent arts-and-entertainment node (Wilton Drive) drawing its first mid-rise projects.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>1650 NE 26th Street</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1650 NE 26th Street came off the market — I cover Sunrise Blvd · Las Olas Blvd. Commercial around here is trading near $208/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $3.12M (~$208/SF) — about a 8.1% cap at market rents. It should rent ~$26/SF — about $398K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$3.12M (~$208/SF). You were asking $2.50M.  •  What does it rent for? ~$26/SF/yr — about $398K/yr gross on 15,003 SF.  •  What cap? ~8.1% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>2500 Wilton Dr</t>
   </si>
   <si>
@@ -1213,18 +1225,6 @@
     <t>What's it worth? Comps support ~$1.93M (~$340/SF). You were asking $2.50M.  •  What does it rent for? ~$7/SF/yr — about $41K/yr gross on 5,664 SF.  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1650 NE 26th Street</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1650 NE 26th Street came off the market — I cover Sunrise Blvd · Las Olas Blvd. Commercial around here is trading near $208/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $3.12M (~$208/SF) — about a 8.1% cap at market rents. It should rent ~$26/SF — about $398K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$3.12M (~$208/SF). You were asking $2.50M.  •  What does it rent for? ~$26/SF/yr — about $398K/yr gross on 15,003 SF.  •  What cap? ~8.1% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>835 NE 3rd Ave</t>
   </si>
   <si>
@@ -1309,6 +1309,18 @@
     <t>What's it worth? Comps support ~$1.54M (~$91/SF). You were asking $2.20M.  •  What does it rent for? ~$20/SF/yr — about $341K/yr gross on 16,875 SF.  •  What cap? ~7.2% implied from lease-vs-sale comps (market benchmark ~6.0–6.75% (blends retail/MF)).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>1210 NE 8th Avenue</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1210 NE 8th Avenue came off the market — I cover Broward Blvd · Sunrise Blvd. Mixed-use around here is trading near $235/SF and leasing around $20/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $1.50M (~$235/SF). It should rent ~$20/SF — about $129K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$1.50M (~$235/SF). You were asking $2.20M.  •  What does it rent for? ~$20/SF/yr — about $129K/yr gross on 6,378 SF.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>1210 NE 8th Ave</t>
   </si>
   <si>
@@ -1324,18 +1336,6 @@
     <t>What's it worth? Comps support ~$2.09M (~$328/SF). You were asking $2.20M.  •  What cap? ~4.3% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1210 NE 8th Avenue</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1210 NE 8th Avenue came off the market — I cover Broward Blvd · Sunrise Blvd. Mixed-use around here is trading near $235/SF and leasing around $20/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $1.50M (~$235/SF). It should rent ~$20/SF — about $129K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$1.50M (~$235/SF). You were asking $2.20M.  •  What does it rent for? ~$20/SF/yr — about $129K/yr gross on 6,378 SF.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>325 NW 25 Street</t>
   </si>
   <si>
@@ -1435,6 +1435,18 @@
     <t>What's it worth? Comps support ~$1.40M (~$270/SF). You were asking $2.00M.  •  What does it rent for? ~$23/SF/yr — about $118K/yr gross on 5,200 SF.  •  What cap? ~6.2% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>2700 E Oakland Park Boulevard</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2700 E Oakland Park Boulevard came off the market — I cover Sunrise Blvd · Oakland Park Blvd. Retail around here is trading near $135/SF and leasing around $28/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.02M (~$135/SF) — about a 12.4% cap at market rents. It should rent ~$28/SF — about $420K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.02M (~$135/SF). You were asking $1.99M.  •  What does it rent for? ~$28/SF/yr — about $420K/yr gross on 15,000 SF.  •  What cap? ~12.4% implied from lease-vs-sale comps (market benchmark ~6.0–6.1%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>1091 NE 4th Avenue</t>
   </si>
   <si>
@@ -1447,18 +1459,6 @@
     <t>What's it worth? Comps support ~$3.40M (~$188/SF). You were asking $1.99M.  •  What does it rent for? ~$26/SF/yr — about $480K/yr gross on 18,100 SF.  •  What cap? ~12.3% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>2700 E Oakland Park Boulevard</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2700 E Oakland Park Boulevard came off the market — I cover Sunrise Blvd · Oakland Park Blvd. Retail around here is trading near $135/SF and leasing around $28/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.02M (~$135/SF) — about a 12.4% cap at market rents. It should rent ~$28/SF — about $420K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.02M (~$135/SF). You were asking $1.99M.  •  What does it rent for? ~$28/SF/yr — about $420K/yr gross on 15,000 SF.  •  What cap? ~12.4% implied from lease-vs-sale comps (market benchmark ~6.0–6.1%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>200-204 NW 17th Court Unit#1-8</t>
   </si>
   <si>
@@ -1582,6 +1582,18 @@
     <t>What's it worth? Comps support ~$2.85M (~$213/SF). You were asking $1.80M.  •  What does it rent for? ~$15/SF/yr — about $206K/yr gross on 13,402 SF.  •  What cap? ~7.3% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>1620 NE 12th Terrace</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1620 NE 12th Terrace came off the market — I cover Oakland Park Blvd. Industrial around here is trading near $263/SF and leasing around $19/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $3.09M (~$263/SF) — about a 6.3% cap at market rents. It should rent ~$19/SF — about $228K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$3.09M (~$263/SF). You were asking $1.80M.  •  What does it rent for? ~$19/SF/yr — about $228K/yr gross on 11,736 SF.  •  What cap? ~6.3% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>1100 NE 18th Court</t>
   </si>
   <si>
@@ -1594,18 +1606,6 @@
     <t>What's it worth? Comps support ~$2.32M (~$253/SF). You were asking $1.80M.  •  What does it rent for? ~$15/SF/yr — about $141K/yr gross on 9,167 SF.  •  What cap? ~5.0% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1620 NE 12th Terrace</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1620 NE 12th Terrace came off the market — I cover Oakland Park Blvd. Industrial around here is trading near $263/SF and leasing around $19/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $3.09M (~$263/SF) — about a 6.3% cap at market rents. It should rent ~$19/SF — about $228K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$3.09M (~$263/SF). You were asking $1.80M.  •  What does it rent for? ~$19/SF/yr — about $228K/yr gross on 11,736 SF.  •  What cap? ~6.3% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>505 SE 20th St Unit#1-5</t>
   </si>
   <si>
@@ -1636,6 +1636,30 @@
     <t>What's it worth? Comps support ~$735K (~$162/SF). You were asking $1.74M.  •  What does it rent for? ~$17/SF/yr — about $77K/yr gross on 4,540 SF.  •  What cap? ~4.2% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>2133 N Dixie Highway</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2133 N Dixie Highway came off the market — I cover Dixie Hwy · Oakland Park Blvd. Commercial around here is trading near $291/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.18M (~$291/SF) — about a 6.0% cap at market rents. It should rent ~$26/SF — about $199K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.18M (~$291/SF). You were asking $1.70M.  •  What does it rent for? ~$26/SF/yr — about $199K/yr gross on 7,497 SF.  •  What cap? ~6.0% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
+    <t>1130 NE 6th Avenue</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1130 NE 6th Avenue came off the market — I cover Dixie Hwy · Oakland Park Blvd. Commercial around here is trading near $220/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.81M (~$220/SF) — about a 10.2% cap at market rents. It should rent ~$26/SF — about $338K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.81M (~$220/SF). You were asking $1.70M.  •  What does it rent for? ~$26/SF/yr — about $338K/yr gross on 12,769 SF.  •  What cap? ~10.2% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>Hi, I saw 511 SE 5th Ave Unit#11 came off the market — I cover Andrews Ave · SE 17th St. Office around here is trading near $166/SF and leasing around $17/SF. I think it can be positioned to actually sell — got two minutes?</t>
   </si>
   <si>
@@ -1645,30 +1669,6 @@
     <t>What's it worth? Comps support ~$720K (~$166/SF). You were asking $1.70M.  •  What does it rent for? ~$17/SF/yr — about $74K/yr gross on 4,340 SF.  •  What cap? ~4.1% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1130 NE 6th Avenue</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1130 NE 6th Avenue came off the market — I cover Dixie Hwy · Oakland Park Blvd. Commercial around here is trading near $220/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.81M (~$220/SF) — about a 10.2% cap at market rents. It should rent ~$26/SF — about $338K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.81M (~$220/SF). You were asking $1.70M.  •  What does it rent for? ~$26/SF/yr — about $338K/yr gross on 12,769 SF.  •  What cap? ~10.2% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>2133 N Dixie Highway</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2133 N Dixie Highway came off the market — I cover Dixie Hwy · Oakland Park Blvd. Commercial around here is trading near $291/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.18M (~$291/SF) — about a 6.0% cap at market rents. It should rent ~$26/SF — about $199K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.18M (~$291/SF). You were asking $1.70M.  •  What does it rent for? ~$26/SF/yr — about $199K/yr gross on 7,497 SF.  •  What cap? ~6.0% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>1415 SW 1st Street Unit#1-8</t>
   </si>
   <si>
@@ -1681,6 +1681,18 @@
     <t>What's it worth? Comps support ~$2.32M (~$168/SF). You were asking $1.70M.  •  What does it rent for? ~$15/SF/yr — about $213K/yr gross on 13,802 SF.  •  What cap? ~8.0% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? Broward's premier office / CBD address — law, finance and wealth-management tenancy.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>2455 E Sunrise Boulevard Unit#Retail Portfolio Sale</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2455 E Sunrise Boulevard Unit#Retail Portfolio Sale came off the market — I cover Sunrise Blvd · Oakland Park Blvd. Commercial around here is trading near $230/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.85M (~$230/SF) — about a 10.5% cap at market rents. It should rent ~$26/SF — about $329K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.85M (~$230/SF). You were asking $1.60M.  •  What does it rent for? ~$26/SF/yr — about $329K/yr gross on 12,398 SF.  •  What cap? ~10.5% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>834 NW 10th Ter</t>
   </si>
   <si>
@@ -1693,24 +1705,36 @@
     <t>What's it worth? Comps support ~$2.40M (~$142/SF). You were asking $1.60M.  •  What does it rent for? ~$19/SF/yr — about $327K/yr gross on 16,875 SF.  •  What cap? ~10.2% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>2455 E Sunrise Boulevard Unit#Retail Portfolio Sale</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2455 E Sunrise Boulevard Unit#Retail Portfolio Sale came off the market — I cover Sunrise Blvd · Oakland Park Blvd. Commercial around here is trading near $230/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.85M (~$230/SF) — about a 10.5% cap at market rents. It should rent ~$26/SF — about $329K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.85M (~$230/SF). You were asking $1.60M.  •  What does it rent for? ~$26/SF/yr — about $329K/yr gross on 12,398 SF.  •  What cap? ~10.5% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>Comps put it around $2.32M (~$166/SF) — about a 8.6% cap at market rents. It should rent ~$15/SF — about $216K/yr gross.</t>
   </si>
   <si>
     <t>What's it worth? Comps support ~$2.32M (~$166/SF). You were asking $1.60M.  •  What does it rent for? ~$15/SF/yr — about $216K/yr gross on 14,000 SF.  •  What cap? ~8.6% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? Broward's premier office / CBD address — law, finance and wealth-management tenancy.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>618 NE 14th Avenue</t>
+  </si>
+  <si>
+    <t>Hi, I saw 618 NE 14th Avenue came off the market — I cover Sunrise Blvd. Multifamily around here is trading near $255/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.44M (~$255/SF) — about a 6.3% cap at market rents. It should rent ~$15/SF — about $147K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.44M (~$255/SF). You were asking $1.50M.  •  What does it rent for? ~$15/SF/yr — about $147K/yr gross on 9,563 SF.  •  What cap? ~6.3% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
+    <t>1100 NE 18th Court Unit#1-8</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1100 NE 18th Court Unit#1-8 came off the market — I cover Dixie Hwy · Oakland Park Blvd. Multifamily around here is trading near $253/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.32M (~$253/SF) — about a 6.0% cap at market rents. It should rent ~$15/SF — about $141K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.32M (~$253/SF). You were asking $1.50M.  •  What does it rent for? ~$15/SF/yr — about $141K/yr gross on 9,167 SF.  •  What cap? ~6.0% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>824 NE 4th St Unit#1-6</t>
   </si>
   <si>
@@ -1723,30 +1747,6 @@
     <t>What's it worth? Comps support ~$2.03M (~$315/SF). You were asking $1.50M.  •  What does it rent for? ~$15/SF/yr — about $99K/yr gross on 6,440 SF.  •  What cap? ~4.2% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1100 NE 18th Court Unit#1-8</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1100 NE 18th Court Unit#1-8 came off the market — I cover Dixie Hwy · Oakland Park Blvd. Multifamily around here is trading near $253/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.32M (~$253/SF) — about a 6.0% cap at market rents. It should rent ~$15/SF — about $141K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.32M (~$253/SF). You were asking $1.50M.  •  What does it rent for? ~$15/SF/yr — about $141K/yr gross on 9,167 SF.  •  What cap? ~6.0% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>618 NE 14th Avenue</t>
-  </si>
-  <si>
-    <t>Hi, I saw 618 NE 14th Avenue came off the market — I cover Sunrise Blvd. Multifamily around here is trading near $255/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.44M (~$255/SF) — about a 6.3% cap at market rents. It should rent ~$15/SF — about $147K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.44M (~$255/SF). You were asking $1.50M.  •  What does it rent for? ~$15/SF/yr — about $147K/yr gross on 9,563 SF.  •  What cap? ~6.3% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>505 SE 20th St Unit#1-6</t>
   </si>
   <si>
@@ -1771,27 +1771,27 @@
     <t>What's it worth? Comps support ~$1.77M (~$149/SF). You were asking $1.43M.  •  What does it rent for? ~$15/SF/yr — about $183K/yr gross on 11,865 SF.  •  What cap? ~8.2% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>1100 NE 18th Ct Unit#1-8</t>
+  </si>
+  <si>
+    <t>Area 3420</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1100 NE 18th Ct Unit#1-8 came off the market — I cover the area. Multifamily around here is trading near $262/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.40M (~$262/SF) — about a 6.4% cap at market rents. It should rent ~$15/SF — about $141K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.40M (~$262/SF). You were asking $1.40M.  •  What does it rent for? ~$15/SF/yr — about $141K/yr gross on 9,167 SF.  •  What cap? ~6.4% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>Comps put it around $2.40M (~$142/SF) — about a 11.7% cap at market rents. It should rent ~$19/SF — about $327K/yr gross.</t>
   </si>
   <si>
     <t>What's it worth? Comps support ~$2.40M (~$142/SF). You were asking $1.40M.  •  What does it rent for? ~$19/SF/yr — about $327K/yr gross on 16,875 SF.  •  What cap? ~11.7% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1100 NE 18th Ct Unit#1-8</t>
-  </si>
-  <si>
-    <t>Area 3420</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1100 NE 18th Ct Unit#1-8 came off the market — I cover the area. Multifamily around here is trading near $262/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.40M (~$262/SF) — about a 6.4% cap at market rents. It should rent ~$15/SF — about $141K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.40M (~$262/SF). You were asking $1.40M.  •  What does it rent for? ~$15/SF/yr — about $141K/yr gross on 9,167 SF.  •  What cap? ~6.4% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>921 NE 3rd Avenue</t>
   </si>
   <si>
@@ -1828,6 +1828,18 @@
     <t>What's it worth? Comps support ~$2.00M (~$276/SF). You were asking $1.40M.  •  What does it rent for? ~$26/SF/yr — about $192K/yr gross on 7,250 SF.  •  What cap? ~7.0% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>1124 NE 5th Avenue Unit#1-6</t>
+  </si>
+  <si>
+    <t>Hi, I saw 1124 NE 5th Avenue Unit#1-6 came off the market — I cover Dixie Hwy · Oakland Park Blvd. Multifamily around here is trading near $206/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.78M (~$206/SF) — about a 9.8% cap at market rents. It should rent ~$15/SF — about $208K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.78M (~$206/SF). You were asking $1.35M.  •  What does it rent for? ~$15/SF/yr — about $208K/yr gross on 13,504 SF.  •  What cap? ~9.8% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>1317 SE 4th Ave</t>
   </si>
   <si>
@@ -1840,18 +1852,6 @@
     <t>What's it worth? Comps support ~$1.08M (~$103/SF). You were asking $1.35M.  •  What does it rent for? ~$17/SF/yr — about $178K/yr gross on 10,500 SF.  •  What cap? ~12.4% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>1124 NE 5th Avenue Unit#1-6</t>
-  </si>
-  <si>
-    <t>Hi, I saw 1124 NE 5th Avenue Unit#1-6 came off the market — I cover Dixie Hwy · Oakland Park Blvd. Multifamily around here is trading near $206/SF and leasing around $15/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.78M (~$206/SF) — about a 9.8% cap at market rents. It should rent ~$15/SF — about $208K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.78M (~$206/SF). You were asking $1.35M.  •  What does it rent for? ~$15/SF/yr — about $208K/yr gross on 13,504 SF.  •  What cap? ~9.8% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>1106 NE 5th Ave Unit#1-5</t>
   </si>
   <si>
@@ -1951,6 +1951,39 @@
     <t>What's it worth? Comps support ~$1.09M (~$124/SF). You were asking $1.20M.  •  What does it rent for? ~$17/SF/yr — about $150K/yr gross on 8,798 SF.  •  What cap? ~11.7% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>Hi, I saw 2600 N Andrews Ave came off the market — I cover Dixie Hwy · Oakland Park Blvd. Mixed-use around here is trading near $192/SF and leasing around $20/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $1.69M (~$192/SF) — about a 6.9% cap at market rents. It should rent ~$20/SF — about $178K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$1.69M (~$192/SF). You were asking $1.20M.  •  What does it rent for? ~$20/SF/yr — about $178K/yr gross on 8,798 SF.  •  What cap? ~6.9% implied from lease-vs-sale comps (market benchmark ~6.0–6.75% (blends retail/MF)).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
+    <t>600 W Oakland Park Blvd</t>
+  </si>
+  <si>
+    <t>Hi, I saw 600 W Oakland Park Blvd came off the market — I cover Oakland Park Blvd · SE 17th St. Retail around here is trading near $166/SF and leasing around $28/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $1.70M (~$166/SF) — about a 14.1% cap at market rents. It should rent ~$28/SF — about $286K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$1.70M (~$166/SF). You were asking $1.20M.  •  What does it rent for? ~$28/SF/yr — about $286K/yr gross on 10,213 SF.  •  What cap? ~14.1% implied from lease-vs-sale comps (market benchmark ~6.0–6.1%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
+    <t>2001 NW 21st Avenue</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2001 NW 21st Avenue came off the market — I cover Broward Blvd · Sunrise Blvd. Commercial around here is trading near $285/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.38M (~$285/SF) — about a 9.4% cap at market rents. It should rent ~$26/SF — about $221K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.38M (~$285/SF). You were asking $1.20M.  •  What does it rent for? ~$26/SF/yr — about $221K/yr gross on 8,333 SF.  •  What cap? ~9.4% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>2001 W State Road 84 #418</t>
   </si>
   <si>
@@ -1963,39 +1996,6 @@
     <t>What's it worth? Comps support ~$3.13M (~$265/SF). You were asking $1.20M.  •  What does it rent for? ~$19/SF/yr — about $229K/yr gross on 11,800 SF.  •  What cap? ~9.5% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>2001 NW 21st Avenue</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2001 NW 21st Avenue came off the market — I cover Broward Blvd · Sunrise Blvd. Commercial around here is trading near $285/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.38M (~$285/SF) — about a 9.4% cap at market rents. It should rent ~$26/SF — about $221K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.38M (~$285/SF). You were asking $1.20M.  •  What does it rent for? ~$26/SF/yr — about $221K/yr gross on 8,333 SF.  •  What cap? ~9.4% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>Hi, I saw 2600 N Andrews Ave came off the market — I cover Dixie Hwy · Oakland Park Blvd. Mixed-use around here is trading near $192/SF and leasing around $20/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $1.69M (~$192/SF) — about a 6.9% cap at market rents. It should rent ~$20/SF — about $178K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$1.69M (~$192/SF). You were asking $1.20M.  •  What does it rent for? ~$20/SF/yr — about $178K/yr gross on 8,798 SF.  •  What cap? ~6.9% implied from lease-vs-sale comps (market benchmark ~6.0–6.75% (blends retail/MF)).  •  How's demand? One of Broward's fastest-emerging urban-infill submarkets, led by public placemaking.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>600 W Oakland Park Blvd</t>
-  </si>
-  <si>
-    <t>Hi, I saw 600 W Oakland Park Blvd came off the market — I cover Oakland Park Blvd · SE 17th St. Retail around here is trading near $166/SF and leasing around $28/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $1.70M (~$166/SF) — about a 14.1% cap at market rents. It should rent ~$28/SF — about $286K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$1.70M (~$166/SF). You were asking $1.20M.  •  What does it rent for? ~$28/SF/yr — about $286K/yr gross on 10,213 SF.  •  What cap? ~14.1% implied from lease-vs-sale comps (market benchmark ~6.0–6.1%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>412 SE 23rd St</t>
   </si>
   <si>
@@ -2128,7 +2128,7 @@
     <t>624 SW 24th Street</t>
   </si>
   <si>
-    <t>Hi, I saw 624 SW 24th Street came off the market — I cover Federal Hwy · SE 17th St. Commercial around here is trading near $329/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
+    <t>Hi, I saw 624 SW 24th Street came off the market — I cover Federal Hwy · SR-84. Commercial around here is trading near $329/SF and leasing around $26/SF. I think it can be positioned to actually sell — got two minutes?</t>
   </si>
   <si>
     <t>Comps put it around $2.08M (~$329/SF) — about a 8.7% cap at market rents. It should rent ~$26/SF — about $168K/yr gross.</t>
@@ -2251,10 +2251,22 @@
     <t>What's it worth? Comps support ~$2.39M (~$354/SF). You were asking $875K.  •  What does it rent for? ~$19/SF/yr — about $131K/yr gross on 6,750 SF.  •  What cap? ~7.5% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>916 NW 9th Avenue</t>
+  </si>
+  <si>
+    <t>Hi, I saw 916 NW 9th Avenue came off the market — I cover Sunrise Blvd. Industrial around here is trading near $231/SF and leasing around $19/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $1.56M (~$231/SF) — about a 7.7% cap at market rents. It should rent ~$19/SF — about $131K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$1.56M (~$231/SF). You were asking $850K.  •  What does it rent for? ~$19/SF/yr — about $131K/yr gross on 6,750 SF.  •  What cap? ~7.7% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>2011 W State Road 84 Unit#232-2</t>
   </si>
   <si>
-    <t>Hi, I saw 2011 W State Road 84 Unit#232-2 came off the market — I cover Federal Hwy · SE 17th St. Industrial around here is trading near $680/SF and leasing around $19/SF. I think it can be positioned to actually sell — got two minutes?</t>
+    <t>Hi, I saw 2011 W State Road 84 Unit#232-2 came off the market — I cover Federal Hwy · SR-84. Industrial around here is trading near $680/SF and leasing around $19/SF. I think it can be positioned to actually sell — got two minutes?</t>
   </si>
   <si>
     <t>Comps put it around $1.36M (~$680/SF). It should rent ~$19/SF — about $39K/yr gross.</t>
@@ -2263,18 +2275,6 @@
     <t>What's it worth? Comps support ~$1.36M (~$680/SF). You were asking $850K.  •  What does it rent for? ~$19/SF/yr — about $39K/yr gross on 2,000 SF.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>916 NW 9th Avenue</t>
-  </si>
-  <si>
-    <t>Hi, I saw 916 NW 9th Avenue came off the market — I cover Sunrise Blvd. Industrial around here is trading near $231/SF and leasing around $19/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $1.56M (~$231/SF) — about a 7.7% cap at market rents. It should rent ~$19/SF — about $131K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$1.56M (~$231/SF). You were asking $850K.  •  What does it rent for? ~$19/SF/yr — about $131K/yr gross on 6,750 SF.  •  What cap? ~7.7% implied from lease-vs-sale comps (market benchmark ~6.0–6.3% (South FL)).  •  How's demand? A CRA-driven, largely opportunity-zone corridor where public subsidy is catalyzing affordable/workforce and mixed-use redevelopment.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>11 SE 13th Street</t>
   </si>
   <si>
@@ -2293,7 +2293,7 @@
     <t>223 SW 17th St</t>
   </si>
   <si>
-    <t>Hi, I saw 223 SW 17th St came off the market — I cover Federal Hwy · SE 17th St. Mixed-use around here is trading near $217/SF and leasing around $20/SF. I think it can be positioned to actually sell — got two minutes?</t>
+    <t>Hi, I saw 223 SW 17th St came off the market — I cover Federal Hwy · SR-84. Mixed-use around here is trading near $217/SF and leasing around $20/SF. I think it can be positioned to actually sell — got two minutes?</t>
   </si>
   <si>
     <t>Comps put it around $1.60M (~$217/SF) — about a 8.1% cap at market rents. It should rent ~$20/SF — about $149K/yr gross.</t>
@@ -2341,21 +2341,21 @@
     <t>2455 E Sunrise Blvd Unit#CU9K-CU9M-CU9L</t>
   </si>
   <si>
+    <t>Area 3300</t>
+  </si>
+  <si>
+    <t>Hi, I saw 2455 E Sunrise Blvd Unit#CU9K-CU9M-CU9L came off the market — I cover Sunrise Blvd. Office around here is trading near $149/SF and leasing around $17/SF. I think it can be positioned to actually sell — got two minutes?</t>
+  </si>
+  <si>
+    <t>Comps put it around $987K (~$149/SF) — about a 14.0% cap at market rents. It should rent ~$17/SF — about $113K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$987K (~$149/SF). You were asking $750K.  •  What does it rent for? ~$17/SF/yr — about $113K/yr gross on 6,624 SF.  •  What cap? ~14.0% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>Area 3350</t>
   </si>
   <si>
-    <t>Hi, I saw 2455 E Sunrise Blvd Unit#CU9K-CU9M-CU9L came off the market — I cover Sunrise Blvd. Office around here is trading near $149/SF and leasing around $17/SF. I think it can be positioned to actually sell — got two minutes?</t>
-  </si>
-  <si>
-    <t>Comps put it around $987K (~$149/SF) — about a 14.0% cap at market rents. It should rent ~$17/SF — about $113K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$987K (~$149/SF). You were asking $750K.  •  What does it rent for? ~$17/SF/yr — about $113K/yr gross on 6,624 SF.  •  What cap? ~14.0% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>Area 3300</t>
-  </si>
-  <si>
     <t>648 W Oakland Park Blvd</t>
   </si>
   <si>
@@ -2575,27 +2575,27 @@
     <t>What's it worth? Comps support ~$4.06M (~$250/SF). You're listed at $4.90M.  •  What does it rent for? ~$26/SF/yr — about $431K/yr gross on 16,250 SF.  •  What cap? ~4.5% implied from lease-vs-sale comps (market benchmark —).  •  How's demand? A walkable, affluent arts-and-entertainment node (Wilton Drive) drawing its first mid-rise projects.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>101-105 SE 26th Street</t>
+  </si>
+  <si>
+    <t>Area 3570</t>
+  </si>
+  <si>
+    <t>Hi — you're on the market at 101-105 SE 26th Street for $4.00M ($212/SF). Comparable multifamily on the area has been closer to $178/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
+  </si>
+  <si>
+    <t>Comps put it around $3.36M (~$178/SF) — about a 4.6% cap at market rents. It should rent ~$15/SF — about $291K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$3.36M (~$178/SF). You're listed at $4.00M.  •  What does it rent for? ~$15/SF/yr — about $291K/yr gross on 18,898 SF.  •  What cap? ~4.6% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>101-105 SE 26 Street</t>
   </si>
   <si>
-    <t>Area 3570</t>
-  </si>
-  <si>
     <t>Hi — you're on the market at 101-105 SE 26 Street for $4.00M ($212/SF). Comparable multifamily on the area has been closer to $178/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
   </si>
   <si>
-    <t>Comps put it around $3.36M (~$178/SF) — about a 4.6% cap at market rents. It should rent ~$15/SF — about $291K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$3.36M (~$178/SF). You're listed at $4.00M.  •  What does it rent for? ~$15/SF/yr — about $291K/yr gross on 18,898 SF.  •  What cap? ~4.6% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
-    <t>101-105 SE 26th Street</t>
-  </si>
-  <si>
-    <t>Hi — you're on the market at 101-105 SE 26th Street for $4.00M ($212/SF). Comparable multifamily on the area has been closer to $178/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
-  </si>
-  <si>
     <t>929 NE 17th Way</t>
   </si>
   <si>
@@ -2665,6 +2665,18 @@
     <t>What's it worth? Comps support ~$2.06M (~$310/SF). You're listed at $2.15M.  •  What does it rent for? ~$15/SF/yr — about $102K/yr gross on 6,633 SF.  •  What cap? ~3.0% implied from lease-vs-sale comps (market benchmark 4.7–5.4% (A ~4.74% · B ~4.92% · C ~5.38%); ~5.6% blended, Yardi ~6.3%).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
+    <t>2745 E Oakland Park Boulevard</t>
+  </si>
+  <si>
+    <t>Hi — you're on the market at 2745 E Oakland Park Boulevard for $2.10M ($280/SF). Comparable commercial on Oakland Park Blvd has been closer to $300/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
+  </si>
+  <si>
+    <t>Comps put it around $2.25M (~$300/SF) — about a 4.8% cap at market rents. It should rent ~$26/SF — about $199K/yr gross.</t>
+  </si>
+  <si>
+    <t>What's it worth? Comps support ~$2.25M (~$300/SF). You're listed at $2.10M.  •  What does it rent for? ~$26/SF/yr — about $199K/yr gross on 7,503 SF.  •  What cap? ~4.8% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
+  </si>
+  <si>
     <t>1327 SE 2nd Ave</t>
   </si>
   <si>
@@ -2677,18 +2689,6 @@
     <t>What's it worth? Comps support ~$1.02M (~$110/SF). You're listed at $2.10M.  •  What does it rent for? ~$17/SF/yr — about $158K/yr gross on 9,289 SF.  •  What cap? ~7.0% implied from lease-vs-sale comps (market benchmark ~6.75–8.0%).  •  How's demand? The region's most active development submarket — a former warehouse district now dense with high-rise multifamily, creative office and ground-floor retail.  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
   </si>
   <si>
-    <t>2745 E Oakland Park Boulevard</t>
-  </si>
-  <si>
-    <t>Hi — you're on the market at 2745 E Oakland Park Boulevard for $2.10M ($280/SF). Comparable commercial on Oakland Park Blvd has been closer to $300/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
-  </si>
-  <si>
-    <t>Comps put it around $2.25M (~$300/SF) — about a 4.8% cap at market rents. It should rent ~$26/SF — about $199K/yr gross.</t>
-  </si>
-  <si>
-    <t>What's it worth? Comps support ~$2.25M (~$300/SF). You're listed at $2.10M.  •  What does it rent for? ~$26/SF/yr — about $199K/yr gross on 7,503 SF.  •  What cap? ~4.8% implied from lease-vs-sale comps (market benchmark —).  •  Why now? 1031 buyers are active, the Live Local Act unlocks density on commercial land, and rising insurance is nudging owners to test the market.</t>
-  </si>
-  <si>
     <t>Hi — you're on the market at 1210 NE 8th Ave for $2.00M ($313/SF). Comparable flex on Wilton Dr · Federal Hwy has been closer to $412/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
   </si>
   <si>
@@ -2767,7 +2767,7 @@
     <t>1200 S Federal Hwy</t>
   </si>
   <si>
-    <t>Hi — you're on the market at 1200 S Federal Hwy for $710K ($387/SF). Comparable retail on Federal Hwy · SE 17th St has been closer to $413/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
+    <t>Hi — you're on the market at 1200 S Federal Hwy for $710K ($387/SF). Comparable retail on Federal Hwy · SR-84 has been closer to $413/SF; I have a read on where it clears and a few active buyers. Worth a quick call?</t>
   </si>
   <si>
     <t>Comps put it around $757K (~$413/SF) — about a 4.3% cap at market rents. It should rent ~$28/SF — about $51K/yr gross.</t>
@@ -3299,6 +3299,9 @@
   </si>
   <si>
     <t>Federal Hwy</t>
+  </si>
+  <si>
+    <t>Wilton Dr · Andrews Ave</t>
   </si>
   <si>
     <t>Oakland Park Blvd · Wilton Dr</t>
@@ -5299,7 +5302,7 @@
         <v>995</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>134</v>
@@ -5388,13 +5391,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D17" s="8">
         <v>5000000</v>
@@ -5624,7 +5627,7 @@
         <v>250</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D27" s="8">
         <v>5000000</v>
@@ -5828,7 +5831,7 @@
         <v>986</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>134</v>
@@ -6242,7 +6245,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B10" s="8">
         <v>22.6</v>
@@ -6271,7 +6274,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B11" s="8">
         <v>7.3</v>
@@ -6647,7 +6650,7 @@
         <v>243</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>930</v>
+        <v>1086</v>
       </c>
       <c r="C27" s="8">
         <v>23</v>
@@ -6697,7 +6700,7 @@
         <v>500</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C29" s="8">
         <v>20</v>
@@ -6723,7 +6726,7 @@
         <v>361</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C30" s="8">
         <v>20</v>
@@ -6775,7 +6778,7 @@
         <v>188</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C32" s="8">
         <v>17</v>
@@ -6801,7 +6804,7 @@
         <v>988</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C33" s="8">
         <v>13.4</v>
@@ -6901,7 +6904,7 @@
         <v>155</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C37" s="8">
         <v>10</v>
@@ -6927,7 +6930,7 @@
         <v>300</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C38" s="8">
         <v>8.199999999999999</v>
@@ -6994,12 +6997,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7024,24 +7027,24 @@
         <v>125</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>149</v>
@@ -7090,7 +7093,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>230</v>
@@ -7116,7 +7119,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>230</v>
@@ -7142,7 +7145,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>230</v>
@@ -7168,7 +7171,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>230</v>
@@ -7194,10 +7197,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>149</v>
@@ -7220,7 +7223,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>188</v>
@@ -7246,7 +7249,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>183</v>
@@ -7272,7 +7275,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>183</v>
@@ -7298,7 +7301,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>250</v>
@@ -7324,7 +7327,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>250</v>
@@ -7350,7 +7353,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>352</v>
@@ -7376,7 +7379,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>352</v>
@@ -7402,7 +7405,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>352</v>
@@ -7428,10 +7431,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>160</v>
@@ -7454,7 +7457,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>194</v>
@@ -7480,7 +7483,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>194</v>
@@ -7506,7 +7509,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>143</v>
@@ -7532,7 +7535,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>143</v>
@@ -7558,7 +7561,7 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>143</v>
@@ -7584,7 +7587,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>143</v>
@@ -7610,7 +7613,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>143</v>
@@ -7636,7 +7639,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>143</v>
@@ -7662,7 +7665,7 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>143</v>
@@ -7688,7 +7691,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>143</v>
@@ -7714,7 +7717,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>143</v>
@@ -7740,7 +7743,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>143</v>
@@ -7766,7 +7769,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>143</v>
@@ -7792,7 +7795,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>243</v>
@@ -7818,13 +7821,13 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>243</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D35" s="7">
         <v>7960</v>
@@ -7844,7 +7847,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>243</v>
@@ -7870,7 +7873,7 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>243</v>
@@ -7896,7 +7899,7 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>243</v>
@@ -7922,7 +7925,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>243</v>
@@ -7948,7 +7951,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>477</v>
@@ -7974,13 +7977,13 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D41" s="7">
         <v>6250</v>
@@ -8000,7 +8003,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>500</v>
@@ -8052,7 +8055,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>255</v>
@@ -8078,7 +8081,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>255</v>
@@ -8130,7 +8133,7 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>161</v>
@@ -8182,7 +8185,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>161</v>
@@ -8208,7 +8211,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>150</v>
@@ -8234,7 +8237,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>300</v>
@@ -8260,7 +8263,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>300</v>
@@ -8286,7 +8289,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>300</v>
@@ -8312,7 +8315,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>300</v>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>178</v>
@@ -8364,7 +8367,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>178</v>
@@ -8390,7 +8393,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>178</v>
@@ -8416,7 +8419,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>178</v>
@@ -8442,13 +8445,13 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D59" s="7">
         <v>15756</v>
@@ -8468,7 +8471,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>395</v>
@@ -8494,7 +8497,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>395</v>
@@ -8520,7 +8523,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>395</v>
@@ -8546,7 +8549,7 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>395</v>
@@ -8572,7 +8575,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>135</v>
@@ -8624,7 +8627,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>135</v>
@@ -8650,7 +8653,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>135</v>
@@ -8676,7 +8679,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>135</v>
@@ -8702,7 +8705,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>135</v>
@@ -8728,7 +8731,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>135</v>
@@ -8754,10 +8757,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>134</v>
@@ -8780,10 +8783,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>160</v>
@@ -8806,10 +8809,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>149</v>
@@ -8850,12 +8853,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8865,7 +8868,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8873,19 +8876,19 @@
         <v>1007</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>1073</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
@@ -8893,19 +8896,19 @@
         <v>160</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
@@ -8913,19 +8916,19 @@
         <v>193</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
@@ -8933,19 +8936,19 @@
         <v>172</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
@@ -8953,19 +8956,19 @@
         <v>149</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
@@ -8973,19 +8976,19 @@
         <v>142</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
@@ -8993,32 +8996,32 @@
         <v>166</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -9027,10 +9030,10 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -9039,10 +9042,10 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -9054,7 +9057,7 @@
         <v>193</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -9063,10 +9066,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -9075,10 +9078,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -9090,7 +9093,7 @@
         <v>142</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -9099,15 +9102,15 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -9116,10 +9119,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -9128,10 +9131,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -9140,10 +9143,10 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -9152,10 +9155,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -9164,15 +9167,15 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -9181,10 +9184,10 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="3" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -9193,10 +9196,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -9205,10 +9208,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="3" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -9217,10 +9220,10 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -9229,15 +9232,15 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -9246,10 +9249,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="3" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -9258,10 +9261,10 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -9270,10 +9273,10 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -9282,10 +9285,10 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="3" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -9294,10 +9297,10 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -9306,10 +9309,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -9318,15 +9321,15 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -9335,10 +9338,10 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -9347,10 +9350,10 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -9359,10 +9362,10 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="3" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -9371,10 +9374,10 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="3" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -9383,10 +9386,10 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="3" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -9395,10 +9398,10 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -9407,15 +9410,15 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -9424,10 +9427,10 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -9436,10 +9439,10 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="3" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -9448,10 +9451,10 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
@@ -9460,10 +9463,10 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="3" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -9472,15 +9475,15 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
@@ -9489,10 +9492,10 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
@@ -9501,10 +9504,10 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="3" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -9513,15 +9516,15 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="58" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
@@ -9530,10 +9533,10 @@
     </row>
     <row r="68" spans="1:6" ht="58" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -9542,10 +9545,10 @@
     </row>
     <row r="69" spans="1:6" ht="58" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -9554,10 +9557,10 @@
     </row>
     <row r="70" spans="1:6" ht="58" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -9566,10 +9569,10 @@
     </row>
     <row r="71" spans="1:6" ht="58" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -9578,10 +9581,10 @@
     </row>
     <row r="72" spans="1:6" ht="58" customHeight="1">
       <c r="A72" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>1296</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>1295</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -9590,10 +9593,10 @@
     </row>
     <row r="73" spans="1:6" ht="58" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -9602,10 +9605,10 @@
     </row>
     <row r="74" spans="1:6" ht="58" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -9614,10 +9617,10 @@
     </row>
     <row r="75" spans="1:6" ht="58" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -9626,127 +9629,127 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="15" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="15" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="15" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="15" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="15" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="15" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="15" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="15" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="15" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="15" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="15" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="15" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="15" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="15" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="15" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="15" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="15" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="15" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="15" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="15" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="15" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="15" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="15" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
   </sheetData>
@@ -9843,12 +9846,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9866,25 +9869,25 @@
         <v>1010</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>1074</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -9914,7 +9917,7 @@
         <v>144</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9944,7 +9947,7 @@
         <v>17</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -9974,7 +9977,7 @@
         <v>28</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -10004,7 +10007,7 @@
         <v>19.4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -10034,7 +10037,7 @@
         <v>20.2</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -10064,12 +10067,12 @@
         <v>144</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B11" s="8">
         <v>365</v>
@@ -10094,12 +10097,12 @@
         <v>22.6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B12" s="8">
         <v>345</v>
@@ -10124,12 +10127,12 @@
         <v>144</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B13" s="8">
         <v>319</v>
@@ -10154,7 +10157,7 @@
         <v>7.3</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -10184,12 +10187,12 @@
         <v>26.5</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
   </sheetData>
@@ -10214,12 +10217,12 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10230,23 +10233,23 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="20" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B4" s="20"/>
       <c r="D4" s="20" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E4" s="20"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="13" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B5" s="21">
         <v>1800000</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E5" s="22">
         <f>($B$6*$B$8*(1-$B$9))</f>
@@ -10255,13 +10258,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="13" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B6" s="23">
         <v>13402</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E6" s="24">
         <f>E5*(1-$B$10)</f>
@@ -10270,11 +10273,11 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="20" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B7" s="20"/>
       <c r="D7" s="3" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E7" s="19">
         <f>E6/$B$5</f>
@@ -10283,13 +10286,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="13" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B8" s="21">
         <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E8" s="24">
         <f>E6/$B$11</f>
@@ -10298,13 +10301,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="13" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B9" s="25">
         <v>0.06</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="E9" s="19">
         <f>$B$14+$B$16/10000</f>
@@ -10313,13 +10316,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="13" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B10" s="25">
         <v>0.42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="E10" s="22">
         <f>$B$5*$B$13</f>
@@ -10328,13 +10331,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="13" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B11" s="26">
         <v>0.055</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="E11" s="24">
         <f>$B$5*(1-$B$13)+$B$5*$B$23</f>
@@ -10343,11 +10346,11 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="20" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B12" s="20"/>
       <c r="D12" s="3" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E12" s="22">
         <f>E10*(E9/12)/(1-(1+E9/12)^-($B$15*12))*12</f>
@@ -10356,13 +10359,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="13" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B13" s="25">
         <v>0.6</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="E13" s="27">
         <f>E6/E12</f>
@@ -10371,13 +10374,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="13" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B14" s="26">
         <v>0.0675</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E14" s="28">
         <f>E6/E10</f>
@@ -10386,13 +10389,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="13" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B15" s="23">
         <v>25</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="E15" s="28">
         <f>(D29-E12)/E11</f>
@@ -10401,13 +10404,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="13" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B16" s="29">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="E16" s="22">
         <f>($B$6*$B$8*(1-$B$9))*(1+$B$19)^$B$21-(($B$6*$B$8*(1-$B$9))*$B$10)*(1+$B$20)^$B$21</f>
@@ -10416,11 +10419,11 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="20" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B17" s="20"/>
       <c r="D17" s="3" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E17" s="24">
         <f>E16/$B$18</f>
@@ -10429,13 +10432,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="13" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B18" s="26">
         <v>0.0575</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E18" s="22">
         <f>E10*((1+E9/12)^($B$15*12)-(1+E9/12)^($B$21*12))/((1+E9/12)^($B$15*12)-1)</f>
@@ -10444,13 +10447,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="13" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B19" s="25">
         <v>0.03</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="E19" s="24">
         <f>E17*(1-$B$22)-E18</f>
@@ -10459,13 +10462,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="13" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B20" s="25">
         <v>0.025</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="E20" s="28">
         <f>IRR(G28:G38)</f>
@@ -10474,13 +10477,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="13" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B21" s="23">
         <v>5</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E21" s="27">
         <f>SUM(G29:G38)/E11</f>
@@ -10489,7 +10492,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="13" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B22" s="25">
         <v>0.02</v>
@@ -10497,7 +10500,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="13" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B23" s="25">
         <v>0.02</v>
@@ -10505,30 +10508,30 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="6" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -10837,21 +10840,21 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -11014,12 +11017,12 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11037,7 +11040,7 @@
         <v>121</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1010</v>
@@ -11046,22 +11049,22 @@
         <v>1072</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>1074</v>
@@ -11072,7 +11075,7 @@
         <v>160</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C5" s="8">
         <v>177</v>
@@ -11107,7 +11110,7 @@
         <v>193</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C6" s="8">
         <v>197</v>
@@ -11142,7 +11145,7 @@
         <v>172</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C7" s="8">
         <v>247</v>
@@ -11177,7 +11180,7 @@
         <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C8" s="8">
         <v>150</v>
@@ -11212,7 +11215,7 @@
         <v>166</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C9" s="8">
         <v>136</v>
@@ -11247,7 +11250,7 @@
         <v>142</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C10" s="8">
         <v>347</v>
@@ -11279,10 +11282,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C11" s="8">
         <v>365</v>
@@ -11314,10 +11317,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C12" s="8">
         <v>345</v>
@@ -11349,10 +11352,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C13" s="8">
         <v>319</v>
@@ -11387,7 +11390,7 @@
         <v>134</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C14" s="8">
         <v>195</v>
@@ -11437,12 +11440,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11461,10 +11464,10 @@
         <v>1072</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>1010</v>
@@ -11615,7 +11618,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B12" s="7">
         <v>8</v>
@@ -11635,7 +11638,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B13" s="7">
         <v>3</v>
@@ -11655,7 +11658,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B14" s="7">
         <v>2</v>
@@ -11906,7 +11909,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="36" customHeight="1">
+    <row r="32" spans="1:2" ht="51" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>95</v>
       </c>
@@ -12841,10 +12844,10 @@
         <v>215</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>136</v>
@@ -12853,22 +12856,22 @@
         <v>137</v>
       </c>
       <c r="G20" s="7">
-        <v>15937</v>
+        <v>8664</v>
       </c>
       <c r="H20" s="8">
         <v>5000000</v>
       </c>
       <c r="I20" s="8">
-        <v>4223000</v>
+        <v>1594000</v>
       </c>
       <c r="J20" s="8">
-        <v>265</v>
+        <v>184</v>
       </c>
       <c r="K20" s="9">
-        <v>0.0432</v>
+        <v>0.0412</v>
       </c>
       <c r="L20" s="8">
-        <v>26.5</v>
+        <v>22.6</v>
       </c>
       <c r="M20" s="4" t="s">
         <v>217</v>
@@ -12888,10 +12891,10 @@
         <v>220</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>136</v>
@@ -12900,22 +12903,22 @@
         <v>137</v>
       </c>
       <c r="G21" s="7">
-        <v>8664</v>
+        <v>15937</v>
       </c>
       <c r="H21" s="8">
         <v>5000000</v>
       </c>
       <c r="I21" s="8">
-        <v>1594000</v>
+        <v>4223000</v>
       </c>
       <c r="J21" s="8">
-        <v>184</v>
+        <v>265</v>
       </c>
       <c r="K21" s="9">
-        <v>0.0412</v>
+        <v>0.0432</v>
       </c>
       <c r="L21" s="8">
-        <v>22.6</v>
+        <v>26.5</v>
       </c>
       <c r="M21" s="4" t="s">
         <v>222</v>
@@ -13029,7 +13032,7 @@
         <v>234</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>188</v>
@@ -13041,22 +13044,22 @@
         <v>137</v>
       </c>
       <c r="G24" s="7">
-        <v>20004</v>
+        <v>14860</v>
       </c>
       <c r="H24" s="8">
         <v>4500000</v>
       </c>
       <c r="I24" s="8">
-        <v>5541000</v>
+        <v>3106000</v>
       </c>
       <c r="J24" s="8">
-        <v>277</v>
+        <v>209</v>
       </c>
       <c r="K24" s="9">
-        <v>0.1182</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>144</v>
+        <v>0.0448</v>
+      </c>
+      <c r="L24" s="8">
+        <v>26.5</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>235</v>
@@ -13076,7 +13079,7 @@
         <v>238</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>188</v>
@@ -13088,22 +13091,22 @@
         <v>137</v>
       </c>
       <c r="G25" s="7">
-        <v>14860</v>
+        <v>20004</v>
       </c>
       <c r="H25" s="8">
         <v>4500000</v>
       </c>
       <c r="I25" s="8">
-        <v>3106000</v>
+        <v>5541000</v>
       </c>
       <c r="J25" s="8">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="K25" s="9">
-        <v>0.0448</v>
-      </c>
-      <c r="L25" s="8">
-        <v>26.5</v>
+        <v>0.1182</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>239</v>
@@ -13167,7 +13170,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>142</v>
@@ -13200,7 +13203,7 @@
         <v>144</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N27" s="4" t="s">
         <v>247</v>
@@ -13496,13 +13499,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>136</v>
@@ -13511,31 +13514,31 @@
         <v>137</v>
       </c>
       <c r="G34" s="7">
-        <v>30093</v>
+        <v>15000</v>
       </c>
       <c r="H34" s="8">
         <v>3600000</v>
       </c>
       <c r="I34" s="8">
-        <v>4183000</v>
+        <v>3120000</v>
       </c>
       <c r="J34" s="8">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="K34" s="9">
-        <v>0.1133</v>
+        <v>0.0565</v>
       </c>
       <c r="L34" s="8">
         <v>26.5</v>
       </c>
       <c r="M34" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="O34" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -13543,13 +13546,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>136</v>
@@ -13558,25 +13561,25 @@
         <v>137</v>
       </c>
       <c r="G35" s="7">
-        <v>15000</v>
+        <v>30093</v>
       </c>
       <c r="H35" s="8">
         <v>3600000</v>
       </c>
       <c r="I35" s="8">
-        <v>3120000</v>
+        <v>4183000</v>
       </c>
       <c r="J35" s="8">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="K35" s="9">
-        <v>0.0565</v>
+        <v>0.1133</v>
       </c>
       <c r="L35" s="8">
         <v>26.5</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="N35" s="4" t="s">
         <v>279</v>
@@ -14486,10 +14489,10 @@
         <v>356</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>149</v>
+        <v>216</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>136</v>
@@ -14498,22 +14501,22 @@
         <v>137</v>
       </c>
       <c r="G55" s="7">
-        <v>7000</v>
+        <v>7960</v>
       </c>
       <c r="H55" s="8">
         <v>2750000</v>
       </c>
       <c r="I55" s="8">
-        <v>1939000</v>
+        <v>2165000</v>
       </c>
       <c r="J55" s="8">
-        <v>277</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>144</v>
+        <v>272</v>
+      </c>
+      <c r="K55" s="9">
+        <v>0.0688</v>
       </c>
       <c r="L55" s="8">
-        <v>19.4</v>
+        <v>22.6</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>357</v>
@@ -14580,10 +14583,10 @@
         <v>365</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>221</v>
+        <v>149</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>136</v>
@@ -14592,22 +14595,22 @@
         <v>137</v>
       </c>
       <c r="G57" s="7">
-        <v>7960</v>
+        <v>7000</v>
       </c>
       <c r="H57" s="8">
         <v>2750000</v>
       </c>
       <c r="I57" s="8">
-        <v>2165000</v>
+        <v>1939000</v>
       </c>
       <c r="J57" s="8">
-        <v>272</v>
-      </c>
-      <c r="K57" s="9">
-        <v>0.0688</v>
+        <v>277</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="L57" s="8">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="M57" s="4" t="s">
         <v>366</v>
@@ -14815,10 +14818,10 @@
         <v>385</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>386</v>
+        <v>134</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>143</v>
+        <v>352</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>136</v>
@@ -14827,31 +14830,31 @@
         <v>137</v>
       </c>
       <c r="G62" s="7">
-        <v>5664</v>
+        <v>15003</v>
       </c>
       <c r="H62" s="8">
         <v>2500000</v>
       </c>
       <c r="I62" s="8">
-        <v>1926000</v>
+        <v>3121000</v>
       </c>
       <c r="J62" s="8">
-        <v>340</v>
-      </c>
-      <c r="K62" s="10" t="s">
-        <v>144</v>
+        <v>208</v>
+      </c>
+      <c r="K62" s="9">
+        <v>0.0813</v>
       </c>
       <c r="L62" s="8">
-        <v>7.3</v>
+        <v>26.5</v>
       </c>
       <c r="M62" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="N62" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="N62" s="4" t="s">
+      <c r="O62" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="O62" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -14859,13 +14862,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="D63" s="4" t="s">
-        <v>352</v>
+        <v>143</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>136</v>
@@ -14874,22 +14877,22 @@
         <v>137</v>
       </c>
       <c r="G63" s="7">
-        <v>15003</v>
+        <v>5664</v>
       </c>
       <c r="H63" s="8">
         <v>2500000</v>
       </c>
       <c r="I63" s="8">
-        <v>3121000</v>
+        <v>1926000</v>
       </c>
       <c r="J63" s="8">
-        <v>208</v>
-      </c>
-      <c r="K63" s="9">
-        <v>0.0813</v>
+        <v>340</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="L63" s="8">
-        <v>26.5</v>
+        <v>7.3</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>391</v>
@@ -14909,7 +14912,7 @@
         <v>394</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>395</v>
@@ -15238,7 +15241,7 @@
         <v>422</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>423</v>
+        <v>166</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>167</v>
@@ -15256,25 +15259,25 @@
         <v>2198672</v>
       </c>
       <c r="I71" s="8">
-        <v>2092000</v>
+        <v>1499000</v>
       </c>
       <c r="J71" s="8">
-        <v>328</v>
-      </c>
-      <c r="K71" s="9">
-        <v>0.0427</v>
-      </c>
-      <c r="L71" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="K71" s="10" t="s">
         <v>144</v>
       </c>
+      <c r="L71" s="8">
+        <v>20.2</v>
+      </c>
       <c r="M71" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="N71" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="N71" s="4" t="s">
+      <c r="O71" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="O71" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="72" spans="1:15">
@@ -15282,10 +15285,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>167</v>
@@ -15303,16 +15306,16 @@
         <v>2198672</v>
       </c>
       <c r="I72" s="8">
-        <v>1499000</v>
+        <v>2092000</v>
       </c>
       <c r="J72" s="8">
-        <v>235</v>
-      </c>
-      <c r="K72" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="K72" s="9">
+        <v>0.0427</v>
+      </c>
+      <c r="L72" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="L72" s="8">
-        <v>20.2</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>428</v>
@@ -15429,7 +15432,7 @@
         <v>160</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>136</v>
@@ -15523,7 +15526,7 @@
         <v>160</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>136</v>
@@ -15661,7 +15664,7 @@
         <v>459</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>460</v>
@@ -15708,10 +15711,10 @@
         <v>464</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>361</v>
+        <v>183</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>136</v>
@@ -15720,22 +15723,22 @@
         <v>137</v>
       </c>
       <c r="G81" s="7">
-        <v>18100</v>
+        <v>15000</v>
       </c>
       <c r="H81" s="8">
         <v>1990000</v>
       </c>
       <c r="I81" s="8">
-        <v>3403000</v>
+        <v>2025000</v>
       </c>
       <c r="J81" s="8">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="K81" s="9">
-        <v>0.1233</v>
+        <v>0.1244</v>
       </c>
       <c r="L81" s="8">
-        <v>26.5</v>
+        <v>28</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>465</v>
@@ -15755,10 +15758,10 @@
         <v>468</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>183</v>
+        <v>361</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>136</v>
@@ -15767,22 +15770,22 @@
         <v>137</v>
       </c>
       <c r="G82" s="7">
-        <v>15000</v>
+        <v>18100</v>
       </c>
       <c r="H82" s="8">
         <v>1990000</v>
       </c>
       <c r="I82" s="8">
-        <v>2025000</v>
+        <v>3403000</v>
       </c>
       <c r="J82" s="8">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="K82" s="9">
-        <v>0.1244</v>
+        <v>0.1233</v>
       </c>
       <c r="L82" s="8">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>469</v>
@@ -16272,10 +16275,10 @@
         <v>513</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>136</v>
@@ -16284,22 +16287,22 @@
         <v>137</v>
       </c>
       <c r="G93" s="7">
-        <v>9167</v>
+        <v>11736</v>
       </c>
       <c r="H93" s="8">
         <v>1800000</v>
       </c>
       <c r="I93" s="8">
-        <v>2319000</v>
+        <v>3087000</v>
       </c>
       <c r="J93" s="8">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K93" s="9">
-        <v>0.05</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="L93" s="8">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="M93" s="4" t="s">
         <v>514</v>
@@ -16319,10 +16322,10 @@
         <v>517</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>136</v>
@@ -16331,22 +16334,22 @@
         <v>137</v>
       </c>
       <c r="G94" s="7">
-        <v>11736</v>
+        <v>9167</v>
       </c>
       <c r="H94" s="8">
         <v>1800000</v>
       </c>
       <c r="I94" s="8">
-        <v>3087000</v>
+        <v>2319000</v>
       </c>
       <c r="J94" s="8">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="K94" s="9">
-        <v>0.06320000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="L94" s="8">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="M94" s="4" t="s">
         <v>518</v>
@@ -16504,13 +16507,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>451</v>
+        <v>531</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>136</v>
@@ -16519,31 +16522,31 @@
         <v>137</v>
       </c>
       <c r="G98" s="7">
-        <v>4340</v>
+        <v>7497</v>
       </c>
       <c r="H98" s="8">
         <v>1700000</v>
       </c>
       <c r="I98" s="8">
-        <v>720000</v>
+        <v>2182000</v>
       </c>
       <c r="J98" s="8">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="K98" s="9">
-        <v>0.0406</v>
+        <v>0.0598</v>
       </c>
       <c r="L98" s="8">
-        <v>17</v>
+        <v>26.5</v>
       </c>
       <c r="M98" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N98" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -16551,7 +16554,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>134</v>
@@ -16584,13 +16587,13 @@
         <v>26.5</v>
       </c>
       <c r="M99" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N99" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="100" spans="1:15">
@@ -16598,13 +16601,13 @@
         <v>96</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>136</v>
@@ -16613,22 +16616,22 @@
         <v>137</v>
       </c>
       <c r="G100" s="7">
-        <v>7497</v>
+        <v>4340</v>
       </c>
       <c r="H100" s="8">
         <v>1700000</v>
       </c>
       <c r="I100" s="8">
-        <v>2182000</v>
+        <v>720000</v>
       </c>
       <c r="J100" s="8">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="K100" s="9">
-        <v>0.0598</v>
+        <v>0.0406</v>
       </c>
       <c r="L100" s="8">
-        <v>26.5</v>
+        <v>17</v>
       </c>
       <c r="M100" s="4" t="s">
         <v>539</v>
@@ -16695,10 +16698,10 @@
         <v>546</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>255</v>
+        <v>183</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>136</v>
@@ -16707,22 +16710,22 @@
         <v>137</v>
       </c>
       <c r="G102" s="7">
-        <v>16875</v>
+        <v>12398</v>
       </c>
       <c r="H102" s="8">
         <v>1600000</v>
       </c>
       <c r="I102" s="8">
-        <v>2396000</v>
+        <v>2852000</v>
       </c>
       <c r="J102" s="8">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="K102" s="9">
-        <v>0.1022</v>
+        <v>0.105</v>
       </c>
       <c r="L102" s="8">
-        <v>19.4</v>
+        <v>26.5</v>
       </c>
       <c r="M102" s="4" t="s">
         <v>547</v>
@@ -16742,10 +16745,10 @@
         <v>550</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>136</v>
@@ -16754,22 +16757,22 @@
         <v>137</v>
       </c>
       <c r="G103" s="7">
-        <v>12398</v>
+        <v>16875</v>
       </c>
       <c r="H103" s="8">
         <v>1600000</v>
       </c>
       <c r="I103" s="8">
-        <v>2852000</v>
+        <v>2396000</v>
       </c>
       <c r="J103" s="8">
-        <v>230</v>
+        <v>142</v>
       </c>
       <c r="K103" s="9">
-        <v>0.105</v>
+        <v>0.1022</v>
       </c>
       <c r="L103" s="8">
-        <v>26.5</v>
+        <v>19.4</v>
       </c>
       <c r="M103" s="4" t="s">
         <v>551</v>
@@ -16839,7 +16842,7 @@
         <v>160</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>395</v>
+        <v>250</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>136</v>
@@ -16848,19 +16851,19 @@
         <v>137</v>
       </c>
       <c r="G105" s="7">
-        <v>6440</v>
+        <v>9563</v>
       </c>
       <c r="H105" s="8">
         <v>1500000</v>
       </c>
       <c r="I105" s="8">
-        <v>2029000</v>
+        <v>2439000</v>
       </c>
       <c r="J105" s="8">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="K105" s="9">
-        <v>0.0421</v>
+        <v>0.0626</v>
       </c>
       <c r="L105" s="8">
         <v>15.4</v>
@@ -16880,13 +16883,13 @@
         <v>102</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>136</v>
@@ -16895,31 +16898,31 @@
         <v>137</v>
       </c>
       <c r="G106" s="7">
-        <v>9167</v>
+        <v>9563</v>
       </c>
       <c r="H106" s="8">
         <v>1500000</v>
       </c>
       <c r="I106" s="8">
-        <v>2319000</v>
+        <v>2439000</v>
       </c>
       <c r="J106" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K106" s="9">
-        <v>0.06</v>
+        <v>0.0626</v>
       </c>
       <c r="L106" s="8">
         <v>15.4</v>
       </c>
       <c r="M106" s="4" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="107" spans="1:15">
@@ -16927,13 +16930,13 @@
         <v>103</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>136</v>
@@ -16942,31 +16945,31 @@
         <v>137</v>
       </c>
       <c r="G107" s="7">
-        <v>9563</v>
+        <v>9167</v>
       </c>
       <c r="H107" s="8">
         <v>1500000</v>
       </c>
       <c r="I107" s="8">
-        <v>2439000</v>
+        <v>2319000</v>
       </c>
       <c r="J107" s="8">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K107" s="9">
-        <v>0.0626</v>
+        <v>0.06</v>
       </c>
       <c r="L107" s="8">
         <v>15.4</v>
       </c>
       <c r="M107" s="4" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="108" spans="1:15">
@@ -16980,7 +16983,7 @@
         <v>160</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>136</v>
@@ -16989,19 +16992,19 @@
         <v>137</v>
       </c>
       <c r="G108" s="7">
-        <v>9563</v>
+        <v>6440</v>
       </c>
       <c r="H108" s="8">
         <v>1500000</v>
       </c>
       <c r="I108" s="8">
-        <v>2439000</v>
+        <v>2029000</v>
       </c>
       <c r="J108" s="8">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="K108" s="9">
-        <v>0.0626</v>
+        <v>0.0421</v>
       </c>
       <c r="L108" s="8">
         <v>15.4</v>
@@ -17115,13 +17118,13 @@
         <v>107</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>255</v>
+        <v>577</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>174</v>
@@ -17130,31 +17133,31 @@
         <v>137</v>
       </c>
       <c r="G111" s="7">
-        <v>16875</v>
+        <v>9167</v>
       </c>
       <c r="H111" s="8">
         <v>1400000</v>
       </c>
       <c r="I111" s="8">
-        <v>2396000</v>
+        <v>2402000</v>
       </c>
       <c r="J111" s="8">
-        <v>142</v>
+        <v>262</v>
       </c>
       <c r="K111" s="9">
-        <v>0.1168</v>
+        <v>0.0643</v>
       </c>
       <c r="L111" s="8">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="N111" s="4" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="112" spans="1:15">
@@ -17162,13 +17165,13 @@
         <v>108</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>579</v>
+        <v>255</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>174</v>
@@ -17177,25 +17180,25 @@
         <v>137</v>
       </c>
       <c r="G112" s="7">
-        <v>9167</v>
+        <v>16875</v>
       </c>
       <c r="H112" s="8">
         <v>1400000</v>
       </c>
       <c r="I112" s="8">
-        <v>2402000</v>
+        <v>2396000</v>
       </c>
       <c r="J112" s="8">
-        <v>262</v>
+        <v>142</v>
       </c>
       <c r="K112" s="9">
-        <v>0.0643</v>
+        <v>0.1168</v>
       </c>
       <c r="L112" s="8">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
       <c r="N112" s="4" t="s">
         <v>581</v>
@@ -17353,10 +17356,10 @@
         <v>595</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>136</v>
@@ -17365,22 +17368,22 @@
         <v>137</v>
       </c>
       <c r="G116" s="7">
-        <v>10500</v>
+        <v>13504</v>
       </c>
       <c r="H116" s="8">
         <v>1350000</v>
       </c>
       <c r="I116" s="8">
-        <v>1082000</v>
+        <v>2782000</v>
       </c>
       <c r="J116" s="8">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="K116" s="9">
-        <v>0.1236</v>
+        <v>0.0982</v>
       </c>
       <c r="L116" s="8">
-        <v>17</v>
+        <v>15.4</v>
       </c>
       <c r="M116" s="4" t="s">
         <v>596</v>
@@ -17400,10 +17403,10 @@
         <v>599</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>136</v>
@@ -17412,22 +17415,22 @@
         <v>137</v>
       </c>
       <c r="G117" s="7">
-        <v>13504</v>
+        <v>10500</v>
       </c>
       <c r="H117" s="8">
         <v>1350000</v>
       </c>
       <c r="I117" s="8">
-        <v>2782000</v>
+        <v>1082000</v>
       </c>
       <c r="J117" s="8">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="K117" s="9">
-        <v>0.0982</v>
+        <v>0.1236</v>
       </c>
       <c r="L117" s="8">
-        <v>15.4</v>
+        <v>17</v>
       </c>
       <c r="M117" s="4" t="s">
         <v>600</v>
@@ -17820,13 +17823,13 @@
         <v>122</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>612</v>
+        <v>143</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>136</v>
@@ -17835,31 +17838,31 @@
         <v>137</v>
       </c>
       <c r="G126" s="7">
-        <v>11800</v>
+        <v>8798</v>
       </c>
       <c r="H126" s="8">
         <v>1200000</v>
       </c>
       <c r="I126" s="8">
-        <v>3127000</v>
+        <v>1689000</v>
       </c>
       <c r="J126" s="8">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="K126" s="9">
-        <v>0.0953</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="L126" s="8">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="M126" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="N126" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="N126" s="4" t="s">
+      <c r="O126" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="O126" s="4" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="127" spans="1:15">
@@ -17867,13 +17870,13 @@
         <v>123</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>136</v>
@@ -17882,31 +17885,31 @@
         <v>137</v>
       </c>
       <c r="G127" s="7">
-        <v>8333</v>
+        <v>8798</v>
       </c>
       <c r="H127" s="8">
         <v>1200000</v>
       </c>
       <c r="I127" s="8">
-        <v>2375000</v>
+        <v>1689000</v>
       </c>
       <c r="J127" s="8">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="K127" s="9">
-        <v>0.0941</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="L127" s="8">
-        <v>26.5</v>
+        <v>20.2</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="128" spans="1:15">
@@ -17914,13 +17917,13 @@
         <v>124</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>143</v>
+        <v>361</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>136</v>
@@ -17929,31 +17932,31 @@
         <v>137</v>
       </c>
       <c r="G128" s="7">
-        <v>8798</v>
+        <v>10213</v>
       </c>
       <c r="H128" s="8">
         <v>1200000</v>
       </c>
       <c r="I128" s="8">
-        <v>1689000</v>
+        <v>1695000</v>
       </c>
       <c r="J128" s="8">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="K128" s="9">
-        <v>0.06859999999999999</v>
+        <v>0.1405</v>
       </c>
       <c r="L128" s="8">
-        <v>20.2</v>
+        <v>28</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
     </row>
     <row r="129" spans="1:15">
@@ -17961,13 +17964,13 @@
         <v>125</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>361</v>
+        <v>167</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>136</v>
@@ -17976,31 +17979,31 @@
         <v>137</v>
       </c>
       <c r="G129" s="7">
-        <v>10213</v>
+        <v>8333</v>
       </c>
       <c r="H129" s="8">
         <v>1200000</v>
       </c>
       <c r="I129" s="8">
-        <v>1695000</v>
+        <v>2375000</v>
       </c>
       <c r="J129" s="8">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="K129" s="9">
-        <v>0.1405</v>
+        <v>0.0941</v>
       </c>
       <c r="L129" s="8">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="M129" s="4" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="130" spans="1:15">
@@ -18008,13 +18011,13 @@
         <v>126</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>143</v>
+        <v>612</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>136</v>
@@ -18023,31 +18026,31 @@
         <v>137</v>
       </c>
       <c r="G130" s="7">
-        <v>8798</v>
+        <v>11800</v>
       </c>
       <c r="H130" s="8">
         <v>1200000</v>
       </c>
       <c r="I130" s="8">
-        <v>1689000</v>
+        <v>3127000</v>
       </c>
       <c r="J130" s="8">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="K130" s="9">
-        <v>0.06859999999999999</v>
+        <v>0.0953</v>
       </c>
       <c r="L130" s="8">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="131" spans="1:15">
@@ -19095,7 +19098,7 @@
         <v>149</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>136</v>
@@ -19104,19 +19107,19 @@
         <v>137</v>
       </c>
       <c r="G153" s="7">
-        <v>2000</v>
+        <v>6750</v>
       </c>
       <c r="H153" s="8">
         <v>850000</v>
       </c>
       <c r="I153" s="8">
-        <v>1360000</v>
+        <v>1559000</v>
       </c>
       <c r="J153" s="8">
-        <v>680</v>
-      </c>
-      <c r="K153" s="10" t="s">
-        <v>144</v>
+        <v>231</v>
+      </c>
+      <c r="K153" s="9">
+        <v>0.077</v>
       </c>
       <c r="L153" s="8">
         <v>19.4</v>
@@ -19142,7 +19145,7 @@
         <v>149</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>255</v>
+        <v>173</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>136</v>
@@ -19151,19 +19154,19 @@
         <v>137</v>
       </c>
       <c r="G154" s="7">
-        <v>6750</v>
+        <v>2000</v>
       </c>
       <c r="H154" s="8">
         <v>850000</v>
       </c>
       <c r="I154" s="8">
-        <v>1559000</v>
+        <v>1360000</v>
       </c>
       <c r="J154" s="8">
-        <v>231</v>
-      </c>
-      <c r="K154" s="9">
-        <v>0.077</v>
+        <v>680</v>
+      </c>
+      <c r="K154" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="L154" s="8">
         <v>19.4</v>
@@ -20445,7 +20448,7 @@
         <v>851</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>143</v>
@@ -20493,7 +20496,7 @@
         <v>160</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>836</v>
@@ -20715,32 +20718,32 @@
         <v>874</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>193</v>
+        <v>134</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>836</v>
       </c>
       <c r="F188" s="4"/>
       <c r="G188" s="7">
-        <v>9289</v>
+        <v>7503</v>
       </c>
       <c r="H188" s="8">
         <v>2100000</v>
       </c>
       <c r="I188" s="8">
-        <v>1022000</v>
+        <v>2251000</v>
       </c>
       <c r="J188" s="8">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="K188" s="9">
-        <v>0.0703</v>
+        <v>0.0484</v>
       </c>
       <c r="L188" s="8">
-        <v>17</v>
+        <v>26.5</v>
       </c>
       <c r="M188" s="4" t="s">
         <v>875</v>
@@ -20760,32 +20763,32 @@
         <v>878</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="E189" s="4" t="s">
         <v>836</v>
       </c>
       <c r="F189" s="4"/>
       <c r="G189" s="7">
-        <v>7503</v>
+        <v>9289</v>
       </c>
       <c r="H189" s="8">
         <v>2100000</v>
       </c>
       <c r="I189" s="8">
-        <v>2251000</v>
+        <v>1022000</v>
       </c>
       <c r="J189" s="8">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="K189" s="9">
-        <v>0.0484</v>
+        <v>0.0703</v>
       </c>
       <c r="L189" s="8">
-        <v>26.5</v>
+        <v>17</v>
       </c>
       <c r="M189" s="4" t="s">
         <v>879</v>
@@ -20802,10 +20805,10 @@
         <v>186</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>243</v>
@@ -20892,7 +20895,7 @@
         <v>188</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>149</v>
@@ -21030,7 +21033,7 @@
         <v>900</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>178</v>
@@ -21288,7 +21291,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>928</v>
@@ -22204,7 +22207,7 @@
         <v>160</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>831</v>
@@ -22294,7 +22297,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>149</v>
@@ -22838,7 +22841,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>160</v>
@@ -22902,7 +22905,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>134</v>
@@ -23190,7 +23193,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>149</v>
@@ -23350,7 +23353,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>134</v>
@@ -23516,7 +23519,7 @@
         <v>160</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>831</v>
@@ -23542,7 +23545,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>149</v>
@@ -23574,13 +23577,13 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>160</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>174</v>
@@ -23606,7 +23609,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>149</v>
@@ -23638,7 +23641,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>134</v>
@@ -23670,7 +23673,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>134</v>
@@ -23734,7 +23737,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>160</v>
@@ -23766,7 +23769,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>160</v>
@@ -23804,7 +23807,7 @@
         <v>160</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>136</v>
@@ -23830,7 +23833,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>149</v>
@@ -23868,7 +23871,7 @@
         <v>160</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>136</v>
@@ -24150,7 +24153,7 @@
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>149</v>
@@ -24406,7 +24409,7 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>172</v>
@@ -24566,7 +24569,7 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>160</v>
@@ -24735,7 +24738,7 @@
         <v>678</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>136</v>
+        <v>836</v>
       </c>
       <c r="E100" s="8">
         <v>1050000</v>
@@ -24799,7 +24802,7 @@
         <v>678</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>836</v>
+        <v>136</v>
       </c>
       <c r="E102" s="8">
         <v>1050000</v>
@@ -24822,7 +24825,7 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>142</v>
@@ -24860,7 +24863,7 @@
         <v>193</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>136</v>
@@ -24892,7 +24895,7 @@
         <v>193</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>136</v>
@@ -24918,10 +24921,10 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>243</v>
@@ -25046,7 +25049,7 @@
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="4" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>160</v>
@@ -25078,7 +25081,7 @@
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="4" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>134</v>
@@ -25238,7 +25241,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>134</v>
@@ -25334,7 +25337,7 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>142</v>
@@ -25526,7 +25529,7 @@
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>134</v>
@@ -25910,7 +25913,7 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="4" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>149</v>
@@ -25974,7 +25977,7 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="4" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>134</v>
@@ -26262,7 +26265,7 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="4" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>172</v>
@@ -26326,25 +26329,25 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="4" t="s">
-        <v>443</v>
+        <v>976</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>136</v>
+        <v>836</v>
       </c>
       <c r="E150" s="8">
-        <v>2050000</v>
+        <v>2695000</v>
       </c>
       <c r="F150" s="8">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="G150" s="8">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="H150" s="11">
         <v>0</v>
@@ -26353,30 +26356,30 @@
         <v>0</v>
       </c>
       <c r="J150" s="11">
-        <v>-49.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="4" t="s">
-        <v>976</v>
+        <v>443</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>836</v>
+        <v>136</v>
       </c>
       <c r="E151" s="8">
-        <v>2695000</v>
+        <v>2050000</v>
       </c>
       <c r="F151" s="8">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="G151" s="8">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="H151" s="11">
         <v>0</v>
@@ -26385,7 +26388,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="11">
-        <v>-0.6</v>
+        <v>-49.9</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -26393,7 +26396,7 @@
         <v>900</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>178</v>
@@ -26614,10 +26617,10 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>167</v>
@@ -26841,7 +26844,7 @@
         <v>851</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>143</v>
@@ -27030,13 +27033,13 @@
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>136</v>
@@ -27286,7 +27289,7 @@
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>193</v>
@@ -27350,10 +27353,10 @@
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="4" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>243</v>
@@ -27446,10 +27449,10 @@
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>143</v>
@@ -27708,7 +27711,7 @@
         <v>160</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>836</v>
@@ -27862,7 +27865,7 @@
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="4" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B198" s="4" t="s">
         <v>149</v>
@@ -27897,7 +27900,7 @@
         <v>459</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>460</v>
@@ -28022,7 +28025,7 @@
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>134</v>
@@ -28150,7 +28153,7 @@
     </row>
     <row r="207" spans="1:10">
       <c r="A207" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>166</v>
@@ -28441,7 +28444,7 @@
         <v>394</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>395</v>
@@ -28534,7 +28537,7 @@
     </row>
     <row r="219" spans="1:10">
       <c r="A219" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>166</v>
@@ -28726,13 +28729,13 @@
     </row>
     <row r="225" spans="1:10">
       <c r="A225" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>836</v>
@@ -28956,7 +28959,7 @@
         <v>134</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>136</v>
@@ -28988,7 +28991,7 @@
         <v>134</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>836</v>
@@ -29046,7 +29049,7 @@
     </row>
     <row r="235" spans="1:10">
       <c r="A235" s="4" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B235" s="4" t="s">
         <v>193</v>
@@ -29305,7 +29308,7 @@
         <v>989</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>250</v>
@@ -29654,10 +29657,10 @@
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>135</v>
@@ -29788,7 +29791,7 @@
         <v>134</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>136</v>
@@ -30238,7 +30241,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B13" s="7">
         <v>8</v>
@@ -30252,7 +30255,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B14" s="7">
         <v>3</v>
@@ -30266,7 +30269,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B15" s="7">
         <v>2</v>
@@ -30638,7 +30641,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B45" s="7">
         <v>2</v>
@@ -30661,7 +30664,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B46" s="7">
         <v>0</v>
@@ -30684,7 +30687,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B47" s="7">
         <v>0</v>
@@ -30870,7 +30873,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B57" s="14">
         <v>25</v>
@@ -30890,7 +30893,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B58" s="14">
         <v>0</v>
@@ -30910,7 +30913,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B59" s="14">
         <v>0</v>
@@ -31137,7 +31140,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B71" s="7">
         <v>1</v>
@@ -31163,7 +31166,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B72" s="7">
         <v>0</v>
@@ -31189,7 +31192,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B73" s="7">
         <v>0</v>
@@ -31402,7 +31405,7 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B83" s="14">
         <v>12.5</v>
@@ -31425,7 +31428,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B84" s="14">
         <v>0</v>
@@ -31448,7 +31451,7 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B85" s="14">
         <v>0</v>
@@ -31901,13 +31904,13 @@
         <v>142</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>134</v>
@@ -32754,7 +32757,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B28" s="7">
         <v>6</v>
@@ -32813,13 +32816,13 @@
         <v>142</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>134</v>
@@ -33597,7 +33600,7 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B53" s="14">
         <v>54.5</v>
@@ -34166,7 +34169,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B80" s="7">
         <v>1</v>
@@ -34649,7 +34652,7 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B105" s="14">
         <v>9.1</v>
@@ -35272,7 +35275,7 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B132" s="7">
         <v>0</v>
@@ -35827,7 +35830,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B157" s="14">
         <v>0</v>
@@ -36302,7 +36305,7 @@
         <v>659</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>160</v>
